--- a/20260713(asset).xlsx
+++ b/20260713(asset).xlsx
@@ -5,21 +5,22 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\블로그\용쨔푸리의 블로그세상\가계부\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\블로그\용쨔푸리의 블로그세상\우리집-통합-재정-대시보드\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="뱅샐현황" sheetId="1" r:id="rId1"/>
+    <sheet name="뱅샐현황(재은)" sheetId="2" r:id="rId1"/>
+    <sheet name="뱅샐현황(영범)" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="136">
   <si>
     <t>항목</t>
   </si>
@@ -304,6 +305,130 @@
   </si>
   <si>
     <t>총 대출 잔액</t>
+  </si>
+  <si>
+    <t>종합매매</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>KB스타통장-저축예금</t>
+  </si>
+  <si>
+    <t>회사대출</t>
+  </si>
+  <si>
+    <t>우리은행 마이너스 통장</t>
+  </si>
+  <si>
+    <t>Sh내가만든통장(스페셜플러스예금)</t>
+  </si>
+  <si>
+    <t>세이프박스</t>
+  </si>
+  <si>
+    <t>씨티원예금</t>
+  </si>
+  <si>
+    <t>우리직장인재테크 저축예금(수수료우대형</t>
+  </si>
+  <si>
+    <t>자립예탁금</t>
+  </si>
+  <si>
+    <t>저축예금</t>
+  </si>
+  <si>
+    <t>토스뱅크 통장</t>
+  </si>
+  <si>
+    <t>하나멤버스 주거래통장</t>
+  </si>
+  <si>
+    <t>네이버페이 머니 - bis0****</t>
+  </si>
+  <si>
+    <t>카카오페이 머니 - 010*****187</t>
+  </si>
+  <si>
+    <t>페이코포인트 - bi*****@naver.com</t>
+  </si>
+  <si>
+    <t>미래에셋전략배분TDF솔루션혼합자산자투자신탁C-Pe</t>
+  </si>
+  <si>
+    <t>한국신종개인용MMF3호_C-P</t>
+  </si>
+  <si>
+    <t>한국전력</t>
+  </si>
+  <si>
+    <t>퀀텀 컴퓨팅</t>
+  </si>
+  <si>
+    <t>메타</t>
+  </si>
+  <si>
+    <t>팔란티어</t>
+  </si>
+  <si>
+    <t>금융상품</t>
+  </si>
+  <si>
+    <t>밸런스 CMA</t>
+  </si>
+  <si>
+    <t>연금저축</t>
+  </si>
+  <si>
+    <t>위탁계좌</t>
+  </si>
+  <si>
+    <t>종합</t>
+  </si>
+  <si>
+    <t>종합투자상품</t>
+  </si>
+  <si>
+    <t>보증금</t>
+  </si>
+  <si>
+    <t>무배당 삼성 올라이프 보장보험(0710.5)</t>
+  </si>
+  <si>
+    <t>무배당 삼성화재 통합보험 수퍼플러스(1202)라이프+</t>
+  </si>
+  <si>
+    <t>무배당굿앤굿어린이종합보험Q(Hi2309)1종(표준형)기본플랜</t>
+  </si>
+  <si>
+    <t>무배당실손의료비보장보험(갱신형)(Hi2307)기본플랜</t>
+  </si>
+  <si>
+    <t>현대해상</t>
+  </si>
+  <si>
+    <t>정상 4건</t>
+  </si>
+  <si>
+    <t>총 4건</t>
+  </si>
+  <si>
+    <t>펀드</t>
+  </si>
+  <si>
+    <t>한국투자증권</t>
+  </si>
+  <si>
+    <t>토스증권</t>
+  </si>
+  <si>
+    <t>총 8개</t>
+  </si>
+  <si>
+    <t>기타은행</t>
+  </si>
+  <si>
+    <t>우리은행</t>
   </si>
 </sst>
 </file>
@@ -641,7 +766,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -702,9 +827,6 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -718,10 +840,26 @@
     <xf numFmtId="3" fontId="2" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -737,16 +875,29 @@
     <xf numFmtId="3" fontId="2" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1053,6 +1204,1490 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:J89"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.75" customWidth="1"/>
+    <col min="2" max="18" width="16.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:9" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="39"/>
+      <c r="E4" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="39"/>
+      <c r="I4" s="36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="41"/>
+      <c r="E5" s="6">
+        <v>36092</v>
+      </c>
+      <c r="F5" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="H5" s="41"/>
+      <c r="I5" s="8">
+        <v>47471370</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="40"/>
+      <c r="C6" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="41"/>
+      <c r="E6" s="6">
+        <v>5</v>
+      </c>
+      <c r="F6" s="54"/>
+      <c r="G6" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="H6" s="41"/>
+      <c r="I6" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="40"/>
+      <c r="C7" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" s="41"/>
+      <c r="E7" s="6">
+        <v>9</v>
+      </c>
+      <c r="F7" s="34"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="40"/>
+      <c r="C8" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="41"/>
+      <c r="E8" s="6">
+        <v>1844</v>
+      </c>
+      <c r="F8" s="34"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="9"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="40"/>
+      <c r="C9" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" s="41"/>
+      <c r="E9" s="6">
+        <v>0</v>
+      </c>
+      <c r="F9" s="34"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="40"/>
+      <c r="C10" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="D10" s="41"/>
+      <c r="E10" s="6">
+        <v>2170345</v>
+      </c>
+      <c r="F10" s="34"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="9"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B11" s="40"/>
+      <c r="C11" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="41"/>
+      <c r="E11" s="6">
+        <v>549</v>
+      </c>
+      <c r="F11" s="34"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="9"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B12" s="40"/>
+      <c r="C12" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="41"/>
+      <c r="E12" s="6">
+        <v>1557980</v>
+      </c>
+      <c r="F12" s="34"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="9"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B13" s="40"/>
+      <c r="C13" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="41"/>
+      <c r="E13" s="6">
+        <v>1009396</v>
+      </c>
+      <c r="F13" s="34"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B14" s="40"/>
+      <c r="C14" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="41"/>
+      <c r="E14" s="6">
+        <v>2259542</v>
+      </c>
+      <c r="F14" s="34"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="9"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B15" s="40"/>
+      <c r="C15" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="41"/>
+      <c r="E15" s="6">
+        <v>0</v>
+      </c>
+      <c r="F15" s="34"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="9"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B16" s="40"/>
+      <c r="C16" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" s="41"/>
+      <c r="E16" s="6">
+        <v>4</v>
+      </c>
+      <c r="F16" s="34"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="9"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B17" s="40"/>
+      <c r="C17" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="41"/>
+      <c r="E17" s="6">
+        <v>100327</v>
+      </c>
+      <c r="F17" s="34"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="9"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="40"/>
+      <c r="C18" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="41"/>
+      <c r="E18" s="6">
+        <v>4960</v>
+      </c>
+      <c r="F18" s="34"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="9"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B19" s="40"/>
+      <c r="C19" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="41"/>
+      <c r="E19" s="6">
+        <v>3971537</v>
+      </c>
+      <c r="F19" s="34"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="9"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B20" s="40"/>
+      <c r="C20" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="41"/>
+      <c r="E20" s="6">
+        <v>387417</v>
+      </c>
+      <c r="F20" s="34"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="9"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B21" s="40"/>
+      <c r="C21" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="41"/>
+      <c r="E21" s="6">
+        <v>313</v>
+      </c>
+      <c r="F21" s="34"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="9"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B22" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="9"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B23" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="41"/>
+      <c r="E23" s="6">
+        <v>1000000</v>
+      </c>
+      <c r="F23" s="34"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="9"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B24" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="9"/>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B25" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="41"/>
+      <c r="E25" s="6">
+        <v>0</v>
+      </c>
+      <c r="F25" s="34"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="9"/>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B26" s="40"/>
+      <c r="C26" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="D26" s="41"/>
+      <c r="E26" s="6">
+        <v>38720</v>
+      </c>
+      <c r="F26" s="34"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="9"/>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B27" s="40"/>
+      <c r="C27" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="41"/>
+      <c r="E27" s="6">
+        <v>0</v>
+      </c>
+      <c r="F27" s="34"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="9"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B28" s="40"/>
+      <c r="C28" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="41"/>
+      <c r="E28" s="6">
+        <v>5945</v>
+      </c>
+      <c r="F28" s="34"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B29" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" s="41"/>
+      <c r="E29" s="6">
+        <v>2702374</v>
+      </c>
+      <c r="F29" s="34"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="9"/>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B30" s="40"/>
+      <c r="C30" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="D30" s="41"/>
+      <c r="E30" s="6">
+        <v>1156893</v>
+      </c>
+      <c r="F30" s="34"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B31" s="40"/>
+      <c r="C31" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" s="41"/>
+      <c r="E31" s="6">
+        <v>1950200</v>
+      </c>
+      <c r="F31" s="34"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="9"/>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B32" s="40"/>
+      <c r="C32" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" s="41"/>
+      <c r="E32" s="6">
+        <v>170250</v>
+      </c>
+      <c r="F32" s="34"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="9"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B33" s="40"/>
+      <c r="C33" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" s="41"/>
+      <c r="E33" s="6">
+        <v>491311.95986152801</v>
+      </c>
+      <c r="F33" s="34"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="9"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B34" s="40"/>
+      <c r="C34" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" s="41"/>
+      <c r="E34" s="6">
+        <v>302954.55181050958</v>
+      </c>
+      <c r="F34" s="34"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="9"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B35" s="40"/>
+      <c r="C35" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="D35" s="41"/>
+      <c r="E35" s="6">
+        <v>230532.45771932101</v>
+      </c>
+      <c r="F35" s="34"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
+      <c r="I35" s="9"/>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B36" s="40"/>
+      <c r="C36" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="D36" s="41"/>
+      <c r="E36" s="6">
+        <v>170250</v>
+      </c>
+      <c r="F36" s="34"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="41"/>
+      <c r="I36" s="9"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B37" s="40"/>
+      <c r="C37" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="D37" s="41"/>
+      <c r="E37" s="6">
+        <v>7118</v>
+      </c>
+      <c r="F37" s="34"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="9"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B38" s="40"/>
+      <c r="C38" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" s="41"/>
+      <c r="E38" s="6">
+        <v>502.54610000000002</v>
+      </c>
+      <c r="F38" s="34"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="41"/>
+      <c r="I38" s="9"/>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B39" s="40"/>
+      <c r="C39" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="D39" s="41"/>
+      <c r="E39" s="6">
+        <v>0</v>
+      </c>
+      <c r="F39" s="34"/>
+      <c r="G39" s="41"/>
+      <c r="H39" s="41"/>
+      <c r="I39" s="9"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B40" s="40"/>
+      <c r="C40" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="D40" s="41"/>
+      <c r="E40" s="6">
+        <v>2180772</v>
+      </c>
+      <c r="F40" s="34"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="41"/>
+      <c r="I40" s="9"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B41" s="40"/>
+      <c r="C41" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="D41" s="41"/>
+      <c r="E41" s="6">
+        <v>1155453.8015999999</v>
+      </c>
+      <c r="F41" s="34"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="41"/>
+      <c r="I41" s="9"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B42" s="40"/>
+      <c r="C42" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="D42" s="41"/>
+      <c r="E42" s="6">
+        <v>2</v>
+      </c>
+      <c r="F42" s="34"/>
+      <c r="G42" s="41"/>
+      <c r="H42" s="41"/>
+      <c r="I42" s="9"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B43" s="40"/>
+      <c r="C43" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="D43" s="41"/>
+      <c r="E43" s="6">
+        <v>2</v>
+      </c>
+      <c r="F43" s="34"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="41"/>
+      <c r="I43" s="9"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B44" s="40"/>
+      <c r="C44" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="41"/>
+      <c r="E44" s="6">
+        <v>4</v>
+      </c>
+      <c r="F44" s="34"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="9"/>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B45" s="40"/>
+      <c r="C45" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D45" s="41"/>
+      <c r="E45" s="6">
+        <v>24</v>
+      </c>
+      <c r="F45" s="34"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="9"/>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B46" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46" s="41"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="9"/>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B47" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C47" s="41"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="41"/>
+      <c r="H47" s="41"/>
+      <c r="I47" s="9"/>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B48" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="D48" s="41"/>
+      <c r="E48" s="6">
+        <v>42000000</v>
+      </c>
+      <c r="F48" s="34"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="41"/>
+      <c r="I48" s="9"/>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B49" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="D49" s="41"/>
+      <c r="E49" s="6">
+        <v>0</v>
+      </c>
+      <c r="F49" s="34"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="9"/>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B50" s="40"/>
+      <c r="C50" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="D50" s="41"/>
+      <c r="E50" s="6">
+        <v>0</v>
+      </c>
+      <c r="F50" s="34"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="9"/>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B51" s="40"/>
+      <c r="C51" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="D51" s="41"/>
+      <c r="E51" s="6">
+        <v>0</v>
+      </c>
+      <c r="F51" s="34"/>
+      <c r="G51" s="41"/>
+      <c r="H51" s="41"/>
+      <c r="I51" s="9"/>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B52" s="40"/>
+      <c r="C52" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52" s="41"/>
+      <c r="E52" s="6">
+        <v>0</v>
+      </c>
+      <c r="F52" s="34"/>
+      <c r="G52" s="41"/>
+      <c r="H52" s="41"/>
+      <c r="I52" s="9"/>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B53" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" s="41"/>
+      <c r="D53" s="41"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="41"/>
+      <c r="H53" s="41"/>
+      <c r="I53" s="9"/>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B54" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54" s="42"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="10">
+        <f>SUM(E5:E53)</f>
+        <v>65063629.317091361</v>
+      </c>
+      <c r="F54" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="G54" s="43"/>
+      <c r="H54" s="43"/>
+      <c r="I54" s="11">
+        <f>SUM(I5:I53)</f>
+        <v>47471370</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B55" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="C55" s="44"/>
+      <c r="D55" s="44"/>
+      <c r="E55" s="44"/>
+      <c r="F55" s="44"/>
+      <c r="G55" s="44"/>
+      <c r="H55" s="44"/>
+      <c r="I55" s="44"/>
+    </row>
+    <row r="56" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="45">
+        <f>E54-I54</f>
+        <v>17592259.317091361</v>
+      </c>
+      <c r="C56" s="45"/>
+      <c r="D56" s="45"/>
+      <c r="E56" s="45"/>
+      <c r="F56" s="45"/>
+      <c r="G56" s="45"/>
+      <c r="H56" s="45"/>
+      <c r="I56" s="45"/>
+    </row>
+    <row r="59" spans="2:9" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="B59" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B60" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B61" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C61" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="D61" s="46"/>
+      <c r="E61" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="F61" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="G61" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="H61" s="33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B62" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C62" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="D62" s="47"/>
+      <c r="E62" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F62" s="17">
+        <v>0</v>
+      </c>
+      <c r="G62" s="18">
+        <v>39472</v>
+      </c>
+      <c r="H62" s="18">
+        <v>69058</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B63" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C63" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="D63" s="47"/>
+      <c r="E63" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F63" s="17">
+        <v>0</v>
+      </c>
+      <c r="G63" s="18">
+        <v>40966</v>
+      </c>
+      <c r="H63" s="18">
+        <v>69456</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B64" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C64" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="D64" s="47"/>
+      <c r="E64" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F64" s="17">
+        <v>989004166</v>
+      </c>
+      <c r="G64" s="18">
+        <v>45189</v>
+      </c>
+      <c r="H64" s="18">
+        <v>56336</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B65" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C65" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="D65" s="47"/>
+      <c r="E65" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F65" s="17">
+        <v>203500000</v>
+      </c>
+      <c r="G65" s="18">
+        <v>45189</v>
+      </c>
+      <c r="H65" s="18">
+        <v>46474</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B66" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="D66" s="49"/>
+      <c r="E66" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="F66" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="G66" s="28"/>
+      <c r="H66" s="20"/>
+    </row>
+    <row r="67" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B67" s="53"/>
+      <c r="C67" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="D67" s="50"/>
+      <c r="E67" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F67" s="32">
+        <f>SUM(F62:F65)</f>
+        <v>1192504166</v>
+      </c>
+      <c r="G67" s="29"/>
+      <c r="H67" s="23"/>
+    </row>
+    <row r="69" spans="2:10" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="B69" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B70" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B71" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C71" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="D71" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="E71" s="46"/>
+      <c r="F71" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="G71" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="H71" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="I71" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="J71" s="33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B72" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C72" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="D72" s="47" t="s">
+        <v>110</v>
+      </c>
+      <c r="E72" s="47"/>
+      <c r="F72" s="17">
+        <v>1946016</v>
+      </c>
+      <c r="G72" s="17">
+        <v>2702374</v>
+      </c>
+      <c r="H72" s="24">
+        <v>38.866998010293848</v>
+      </c>
+      <c r="I72" s="18"/>
+      <c r="J72" s="18"/>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B73" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C73" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="D73" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="E73" s="47"/>
+      <c r="F73" s="17">
+        <v>1000001</v>
+      </c>
+      <c r="G73" s="17">
+        <v>1156893</v>
+      </c>
+      <c r="H73" s="24">
+        <v>15.689184310815691</v>
+      </c>
+      <c r="I73" s="18"/>
+      <c r="J73" s="18"/>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B74" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="D74" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="E74" s="47"/>
+      <c r="F74" s="17">
+        <v>1831849</v>
+      </c>
+      <c r="G74" s="17">
+        <v>1950200</v>
+      </c>
+      <c r="H74" s="24">
+        <v>6.4607399409012416</v>
+      </c>
+      <c r="I74" s="18"/>
+      <c r="J74" s="18"/>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B75" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C75" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="D75" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="E75" s="47"/>
+      <c r="F75" s="17">
+        <v>143500</v>
+      </c>
+      <c r="G75" s="17">
+        <v>170250</v>
+      </c>
+      <c r="H75" s="24">
+        <v>18.641114982578401</v>
+      </c>
+      <c r="I75" s="18"/>
+      <c r="J75" s="18"/>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B76" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C76" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="D76" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="E76" s="47"/>
+      <c r="F76" s="17">
+        <v>1064609</v>
+      </c>
+      <c r="G76" s="17">
+        <v>491311.95986152801</v>
+      </c>
+      <c r="H76" s="24">
+        <v>-53.850478451569742</v>
+      </c>
+      <c r="I76" s="18"/>
+      <c r="J76" s="18"/>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B77" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C77" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="D77" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="E77" s="47"/>
+      <c r="F77" s="17">
+        <v>297847</v>
+      </c>
+      <c r="G77" s="17">
+        <v>302954.55181050958</v>
+      </c>
+      <c r="H77" s="24">
+        <v>1.714823990340538</v>
+      </c>
+      <c r="I77" s="18"/>
+      <c r="J77" s="18"/>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B78" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C78" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="D78" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="E78" s="47"/>
+      <c r="F78" s="17">
+        <v>296496</v>
+      </c>
+      <c r="G78" s="17">
+        <v>230532.45771932101</v>
+      </c>
+      <c r="H78" s="24">
+        <v>-22.247700569545291</v>
+      </c>
+      <c r="I78" s="18"/>
+      <c r="J78" s="18"/>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B79" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C79" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="D79" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="E79" s="47"/>
+      <c r="F79" s="17">
+        <v>296500</v>
+      </c>
+      <c r="G79" s="17">
+        <v>170250</v>
+      </c>
+      <c r="H79" s="24">
+        <v>-42.580101180438447</v>
+      </c>
+      <c r="I79" s="18"/>
+      <c r="J79" s="18"/>
+    </row>
+    <row r="80" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B80" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C80" s="28"/>
+      <c r="D80" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="E80" s="49"/>
+      <c r="F80" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="G80" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="H80" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="I80" s="28"/>
+      <c r="J80" s="20"/>
+    </row>
+    <row r="81" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B81" s="48"/>
+      <c r="C81" s="29"/>
+      <c r="D81" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E81" s="50"/>
+      <c r="F81" s="32">
+        <f>SUM(F72:F79)</f>
+        <v>6876818</v>
+      </c>
+      <c r="G81" s="32">
+        <f>SUM(G72:G79)</f>
+        <v>7174765.969391359</v>
+      </c>
+      <c r="H81" s="25">
+        <f>(SUM(G72:G79) - SUM(F72:F79)) * 100 / IF(SUM(F72:F79), SUM(F72:F79), 1)</f>
+        <v>4.332642937349207</v>
+      </c>
+      <c r="I81" s="29"/>
+      <c r="J81" s="23"/>
+    </row>
+    <row r="83" spans="2:10" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="B83" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B84" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B85" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C85" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="D85" s="51" t="s">
+        <v>6</v>
+      </c>
+      <c r="E85" s="51"/>
+      <c r="F85" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="G85" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="H85" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="I85" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="J85" s="30" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B86" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C86" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D86" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="E86" s="47"/>
+      <c r="F86" s="17">
+        <v>0</v>
+      </c>
+      <c r="G86" s="17">
+        <v>47471370</v>
+      </c>
+      <c r="H86" s="31"/>
+      <c r="I86" s="18">
+        <v>44505</v>
+      </c>
+      <c r="J86" s="18">
+        <v>44505</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B87" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C87" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="D87" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="E87" s="47"/>
+      <c r="F87" s="17">
+        <v>40000000</v>
+      </c>
+      <c r="G87" s="17">
+        <v>0</v>
+      </c>
+      <c r="H87" s="31">
+        <v>4.87</v>
+      </c>
+      <c r="I87" s="18">
+        <v>43889</v>
+      </c>
+      <c r="J87" s="18">
+        <v>46450</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B88" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C88" s="28"/>
+      <c r="D88" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="E88" s="49"/>
+      <c r="F88" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="G88" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="H88" s="28"/>
+      <c r="I88" s="28"/>
+      <c r="J88" s="20"/>
+    </row>
+    <row r="89" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B89" s="48"/>
+      <c r="C89" s="29"/>
+      <c r="D89" s="52">
+        <f>SUM(2)</f>
+        <v>2</v>
+      </c>
+      <c r="E89" s="52"/>
+      <c r="F89" s="32">
+        <f>SUM(F86:F87)</f>
+        <v>40000000</v>
+      </c>
+      <c r="G89" s="32">
+        <f>SUM(G86:G87)</f>
+        <v>47471370</v>
+      </c>
+      <c r="H89" s="29"/>
+      <c r="I89" s="29"/>
+      <c r="J89" s="23"/>
+    </row>
+  </sheetData>
+  <mergeCells count="137">
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="D88:E88"/>
+    <mergeCell ref="D89:E89"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="D80:E80"/>
+    <mergeCell ref="D81:E81"/>
+    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="D77:E77"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="D79:E79"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="B29:B45"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="B5:B21"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G4:H4"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:J68"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1071,569 +2706,569 @@
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="43" t="s">
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="44"/>
+      <c r="D4" s="39"/>
       <c r="E4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="44" t="s">
+      <c r="G4" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="44"/>
+      <c r="H4" s="39"/>
       <c r="I4" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="36"/>
+      <c r="D5" s="41"/>
       <c r="E5" s="6">
         <v>3931685</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="G5" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="36"/>
+      <c r="H5" s="41"/>
       <c r="I5" s="8">
         <v>600000000</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="41"/>
-      <c r="C6" s="36" t="s">
+      <c r="B6" s="40"/>
+      <c r="C6" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="36"/>
+      <c r="D6" s="41"/>
       <c r="E6" s="6">
         <v>13090630</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
       <c r="I6" s="9"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="41"/>
-      <c r="C7" s="36" t="s">
+      <c r="B7" s="40"/>
+      <c r="C7" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="36"/>
+      <c r="D7" s="41"/>
       <c r="E7" s="6">
         <v>41</v>
       </c>
       <c r="F7" s="5"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
       <c r="I7" s="9"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="41"/>
-      <c r="C8" s="36" t="s">
+      <c r="B8" s="40"/>
+      <c r="C8" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="36"/>
+      <c r="D8" s="41"/>
       <c r="E8" s="6">
         <v>2</v>
       </c>
       <c r="F8" s="5"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
       <c r="I8" s="9"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="41"/>
-      <c r="C9" s="36" t="s">
+      <c r="B9" s="40"/>
+      <c r="C9" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="36"/>
+      <c r="D9" s="41"/>
       <c r="E9" s="6">
         <v>3269297</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
       <c r="I9" s="9"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="41"/>
-      <c r="C10" s="36" t="s">
+      <c r="B10" s="40"/>
+      <c r="C10" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="36"/>
+      <c r="D10" s="41"/>
       <c r="E10" s="6">
         <v>1107</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
       <c r="I10" s="9"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="41"/>
-      <c r="C11" s="36" t="s">
+      <c r="B11" s="40"/>
+      <c r="C11" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="41"/>
       <c r="E11" s="6">
         <v>126</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
       <c r="I11" s="9"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="41"/>
-      <c r="C12" s="36" t="s">
+      <c r="B12" s="40"/>
+      <c r="C12" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="36"/>
+      <c r="D12" s="41"/>
       <c r="E12" s="6">
         <v>6449648</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
       <c r="I12" s="9"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="41"/>
-      <c r="C13" s="36" t="s">
+      <c r="B13" s="40"/>
+      <c r="C13" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="36"/>
+      <c r="D13" s="41"/>
       <c r="E13" s="6">
         <v>7000</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
       <c r="I13" s="9"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="41"/>
-      <c r="C14" s="36" t="s">
+      <c r="B14" s="40"/>
+      <c r="C14" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="36"/>
+      <c r="D14" s="41"/>
       <c r="E14" s="6">
         <v>41506</v>
       </c>
       <c r="F14" s="5"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
       <c r="I14" s="9"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
       <c r="E15" s="6"/>
       <c r="F15" s="5"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
       <c r="I15" s="9"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="36"/>
+      <c r="D16" s="41"/>
       <c r="E16" s="6">
         <v>0</v>
       </c>
       <c r="F16" s="5"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
       <c r="I16" s="9"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="36"/>
+      <c r="D17" s="41"/>
       <c r="E17" s="6">
         <v>100000</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
       <c r="I17" s="9"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="36"/>
+      <c r="D18" s="41"/>
       <c r="E18" s="6">
         <v>0</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
       <c r="I18" s="9"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="41"/>
-      <c r="C19" s="36" t="s">
+      <c r="B19" s="40"/>
+      <c r="C19" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="36"/>
+      <c r="D19" s="41"/>
       <c r="E19" s="6">
         <v>0</v>
       </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
       <c r="I19" s="9"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="41"/>
-      <c r="C20" s="36" t="s">
+      <c r="B20" s="40"/>
+      <c r="C20" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="36"/>
+      <c r="D20" s="41"/>
       <c r="E20" s="6">
         <v>12000</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
       <c r="I20" s="9"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B21" s="41"/>
-      <c r="C21" s="36" t="s">
+      <c r="B21" s="40"/>
+      <c r="C21" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="36"/>
+      <c r="D21" s="41"/>
       <c r="E21" s="6">
         <v>0</v>
       </c>
       <c r="F21" s="5"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
       <c r="I21" s="9"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C22" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="36"/>
+      <c r="D22" s="41"/>
       <c r="E22" s="6">
         <v>1919980</v>
       </c>
       <c r="F22" s="5"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
       <c r="I22" s="9"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="41"/>
-      <c r="C23" s="36" t="s">
+      <c r="B23" s="40"/>
+      <c r="C23" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="36"/>
+      <c r="D23" s="41"/>
       <c r="E23" s="6">
         <v>1726080</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
       <c r="I23" s="9"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B24" s="41"/>
-      <c r="C24" s="36" t="s">
+      <c r="B24" s="40"/>
+      <c r="C24" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="36"/>
+      <c r="D24" s="41"/>
       <c r="E24" s="6">
         <v>20105</v>
       </c>
       <c r="F24" s="5"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
       <c r="I24" s="9"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B25" s="41"/>
-      <c r="C25" s="36" t="s">
+      <c r="B25" s="40"/>
+      <c r="C25" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="36"/>
+      <c r="D25" s="41"/>
       <c r="E25" s="6">
         <v>446955.17499999999</v>
       </c>
       <c r="F25" s="5"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
+      <c r="G25" s="41"/>
+      <c r="H25" s="41"/>
       <c r="I25" s="9"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B26" s="41"/>
-      <c r="C26" s="36" t="s">
+      <c r="B26" s="40"/>
+      <c r="C26" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="D26" s="36"/>
+      <c r="D26" s="41"/>
       <c r="E26" s="6">
         <v>3481.8249999999998</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
       <c r="I26" s="9"/>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B27" s="41"/>
-      <c r="C27" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" s="36"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" s="41"/>
       <c r="E27" s="6">
         <v>282</v>
       </c>
       <c r="F27" s="5"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
       <c r="I27" s="9"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B28" s="41"/>
-      <c r="C28" s="36" t="s">
+      <c r="B28" s="40"/>
+      <c r="C28" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="D28" s="36"/>
+      <c r="D28" s="41"/>
       <c r="E28" s="6">
         <v>693121</v>
       </c>
       <c r="F28" s="5"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="36"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
       <c r="I28" s="9"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B29" s="41"/>
-      <c r="C29" s="36" t="s">
+      <c r="B29" s="40"/>
+      <c r="C29" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="36"/>
+      <c r="D29" s="41"/>
       <c r="E29" s="6">
         <v>1</v>
       </c>
       <c r="F29" s="5"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="36"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
       <c r="I29" s="9"/>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
       <c r="E30" s="6"/>
       <c r="F30" s="5"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
       <c r="I30" s="9"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="36"/>
-      <c r="D31" s="36"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
       <c r="E31" s="6"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
       <c r="I31" s="9"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
       <c r="E32" s="6"/>
       <c r="F32" s="5"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
+      <c r="G32" s="41"/>
+      <c r="H32" s="41"/>
       <c r="I32" s="9"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B33" s="41" t="s">
+      <c r="B33" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="D33" s="36"/>
+      <c r="D33" s="41"/>
       <c r="E33" s="6">
         <v>0</v>
       </c>
       <c r="F33" s="5"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
       <c r="I33" s="9"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B34" s="41"/>
-      <c r="C34" s="36" t="s">
+      <c r="B34" s="40"/>
+      <c r="C34" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="D34" s="36"/>
+      <c r="D34" s="41"/>
       <c r="E34" s="6">
         <v>0</v>
       </c>
       <c r="F34" s="5"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
       <c r="I34" s="9"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B35" s="41"/>
-      <c r="C35" s="36" t="s">
+      <c r="B35" s="40"/>
+      <c r="C35" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="D35" s="36"/>
+      <c r="D35" s="41"/>
       <c r="E35" s="6">
         <v>0</v>
       </c>
       <c r="F35" s="5"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
       <c r="I35" s="9"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B36" s="41"/>
-      <c r="C36" s="36" t="s">
+      <c r="B36" s="40"/>
+      <c r="C36" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="D36" s="36"/>
+      <c r="D36" s="41"/>
       <c r="E36" s="6">
         <v>0</v>
       </c>
       <c r="F36" s="5"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
+      <c r="G36" s="41"/>
+      <c r="H36" s="41"/>
       <c r="I36" s="9"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B37" s="41"/>
-      <c r="C37" s="36" t="s">
+      <c r="B37" s="40"/>
+      <c r="C37" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="D37" s="36"/>
+      <c r="D37" s="41"/>
       <c r="E37" s="6">
         <v>0</v>
       </c>
       <c r="F37" s="5"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="36"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
       <c r="I37" s="9"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
       <c r="E38" s="6"/>
       <c r="F38" s="5"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="36"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="41"/>
       <c r="I38" s="9"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="37" t="s">
+      <c r="B39" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="C39" s="37"/>
-      <c r="D39" s="37"/>
+      <c r="C39" s="42"/>
+      <c r="D39" s="42"/>
       <c r="E39" s="10">
         <f>SUM(E5:E38)</f>
         <v>31713048</v>
       </c>
-      <c r="F39" s="38" t="s">
+      <c r="F39" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="G39" s="38"/>
-      <c r="H39" s="38"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
       <c r="I39" s="11">
         <f>SUM(I5:I38)</f>
         <v>600000000</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="39" t="s">
+      <c r="B40" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="39"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="39"/>
-      <c r="F40" s="39"/>
-      <c r="G40" s="39"/>
-      <c r="H40" s="39"/>
-      <c r="I40" s="39"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="44"/>
+      <c r="F40" s="44"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="44"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B41" s="40">
+      <c r="B41" s="45">
         <f>E39-I39</f>
         <v>-568286952</v>
       </c>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="40"/>
-      <c r="F41" s="40"/>
-      <c r="G41" s="40"/>
-      <c r="H41" s="40"/>
-      <c r="I41" s="40"/>
+      <c r="C41" s="45"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="45"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="45"/>
+      <c r="I41" s="45"/>
     </row>
     <row r="44" spans="2:9" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
@@ -1649,10 +3284,10 @@
       <c r="B46" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C46" s="35" t="s">
+      <c r="C46" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="D46" s="35"/>
+      <c r="D46" s="46"/>
       <c r="E46" s="13" t="s">
         <v>56</v>
       </c>
@@ -1670,10 +3305,10 @@
       <c r="B47" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C47" s="32" t="s">
+      <c r="C47" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="D47" s="32"/>
+      <c r="D47" s="47"/>
       <c r="E47" s="16" t="s">
         <v>61</v>
       </c>
@@ -1691,10 +3326,10 @@
       <c r="B48" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C48" s="32" t="s">
+      <c r="C48" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="D48" s="32"/>
+      <c r="D48" s="47"/>
       <c r="E48" s="16" t="s">
         <v>61</v>
       </c>
@@ -1712,10 +3347,10 @@
       <c r="B49" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C49" s="32" t="s">
+      <c r="C49" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="D49" s="32"/>
+      <c r="D49" s="47"/>
       <c r="E49" s="16" t="s">
         <v>61</v>
       </c>
@@ -1733,10 +3368,10 @@
       <c r="B50" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C50" s="32" t="s">
+      <c r="C50" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="D50" s="32"/>
+      <c r="D50" s="47"/>
       <c r="E50" s="16" t="s">
         <v>61</v>
       </c>
@@ -1754,10 +3389,10 @@
       <c r="B51" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C51" s="32" t="s">
+      <c r="C51" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="D51" s="32"/>
+      <c r="D51" s="47"/>
       <c r="E51" s="16" t="s">
         <v>61</v>
       </c>
@@ -1772,13 +3407,13 @@
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B52" s="34" t="s">
+      <c r="B52" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C52" s="29" t="s">
+      <c r="C52" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="D52" s="29"/>
+      <c r="D52" s="49"/>
       <c r="E52" s="19" t="s">
         <v>64</v>
       </c>
@@ -1789,11 +3424,11 @@
       <c r="H52" s="20"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B53" s="34"/>
-      <c r="C53" s="30" t="s">
+      <c r="B53" s="53"/>
+      <c r="C53" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="D53" s="30"/>
+      <c r="D53" s="50"/>
       <c r="E53" s="21" t="s">
         <v>67</v>
       </c>
@@ -1821,10 +3456,10 @@
       <c r="C57" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D57" s="35" t="s">
+      <c r="D57" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E57" s="35"/>
+      <c r="E57" s="46"/>
       <c r="F57" s="13" t="s">
         <v>71</v>
       </c>
@@ -1848,10 +3483,10 @@
       <c r="C58" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="D58" s="32" t="s">
+      <c r="D58" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="E58" s="32"/>
+      <c r="E58" s="47"/>
       <c r="F58" s="17">
         <v>1277189</v>
       </c>
@@ -1871,10 +3506,10 @@
       <c r="C59" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="D59" s="32" t="s">
+      <c r="D59" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="E59" s="32"/>
+      <c r="E59" s="47"/>
       <c r="F59" s="17">
         <v>1737959</v>
       </c>
@@ -1888,14 +3523,14 @@
       <c r="J59" s="18"/>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B60" s="28" t="s">
+      <c r="B60" s="48" t="s">
         <v>1</v>
       </c>
       <c r="C60" s="19"/>
-      <c r="D60" s="29" t="s">
+      <c r="D60" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="E60" s="29"/>
+      <c r="E60" s="49"/>
       <c r="F60" s="19" t="s">
         <v>78</v>
       </c>
@@ -1909,12 +3544,12 @@
       <c r="J60" s="20"/>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B61" s="28"/>
+      <c r="B61" s="48"/>
       <c r="C61" s="21"/>
-      <c r="D61" s="30" t="s">
+      <c r="D61" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="E61" s="30"/>
+      <c r="E61" s="50"/>
       <c r="F61" s="22">
         <f>SUM(F58:F59)</f>
         <v>3015148</v>
@@ -1947,10 +3582,10 @@
       <c r="C65" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="D65" s="31" t="s">
+      <c r="D65" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="E65" s="31"/>
+      <c r="E65" s="51"/>
       <c r="F65" s="27" t="s">
         <v>85</v>
       </c>
@@ -1974,10 +3609,10 @@
       <c r="C66" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D66" s="32" t="s">
+      <c r="D66" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="E66" s="32"/>
+      <c r="E66" s="47"/>
       <c r="F66" s="17">
         <v>600000000</v>
       </c>
@@ -1995,14 +3630,14 @@
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B67" s="28" t="s">
+      <c r="B67" s="48" t="s">
         <v>1</v>
       </c>
       <c r="C67" s="19"/>
-      <c r="D67" s="29" t="s">
+      <c r="D67" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="E67" s="29"/>
+      <c r="E67" s="49"/>
       <c r="F67" s="19" t="s">
         <v>93</v>
       </c>
@@ -2014,13 +3649,13 @@
       <c r="J67" s="20"/>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B68" s="28"/>
+      <c r="B68" s="48"/>
       <c r="C68" s="21"/>
-      <c r="D68" s="33">
+      <c r="D68" s="52">
         <f>SUM(1)</f>
         <v>1</v>
       </c>
-      <c r="E68" s="33"/>
+      <c r="E68" s="52"/>
       <c r="F68" s="22">
         <f>SUM(F66)</f>
         <v>600000000</v>
@@ -2035,6 +3670,90 @@
     </row>
   </sheetData>
   <mergeCells count="100">
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="B33:B37"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="B22:B29"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="F3:I3"/>
     <mergeCell ref="C4:D4"/>
@@ -2051,90 +3770,6 @@
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="G14:H14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="B22:B29"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="B33:B37"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="B40:I40"/>
-    <mergeCell ref="B41:I41"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D59:E59"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/20260713(asset).xlsx
+++ b/20260713(asset).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="뱅샐현황(재은)" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="143">
   <si>
     <t>항목</t>
   </si>
@@ -326,109 +326,141 @@
     <t>세이프박스</t>
   </si>
   <si>
+    <t>우리직장인재테크 저축예금(수수료우대형</t>
+  </si>
+  <si>
+    <t>토스뱅크 통장</t>
+  </si>
+  <si>
+    <t>하나멤버스 주거래통장</t>
+  </si>
+  <si>
+    <t>네이버페이 머니 - bis0****</t>
+  </si>
+  <si>
+    <t>카카오페이 머니 - 010*****187</t>
+  </si>
+  <si>
+    <t>페이코포인트 - bi*****@naver.com</t>
+  </si>
+  <si>
+    <t>미래에셋전략배분TDF솔루션혼합자산자투자신탁C-Pe</t>
+  </si>
+  <si>
+    <t>한국신종개인용MMF3호_C-P</t>
+  </si>
+  <si>
+    <t>한국전력</t>
+  </si>
+  <si>
+    <t>퀀텀 컴퓨팅</t>
+  </si>
+  <si>
+    <t>메타</t>
+  </si>
+  <si>
+    <t>팔란티어</t>
+  </si>
+  <si>
+    <t>금융상품</t>
+  </si>
+  <si>
+    <t>밸런스 CMA</t>
+  </si>
+  <si>
+    <t>연금저축</t>
+  </si>
+  <si>
+    <t>위탁계좌</t>
+  </si>
+  <si>
+    <t>종합투자상품</t>
+  </si>
+  <si>
+    <t>보증금</t>
+  </si>
+  <si>
+    <t>무배당 삼성 올라이프 보장보험(0710.5)</t>
+  </si>
+  <si>
+    <t>무배당 삼성화재 통합보험 수퍼플러스(1202)라이프+</t>
+  </si>
+  <si>
+    <t>무배당굿앤굿어린이종합보험Q(Hi2309)1종(표준형)기본플랜</t>
+  </si>
+  <si>
+    <t>무배당실손의료비보장보험(갱신형)(Hi2307)기본플랜</t>
+  </si>
+  <si>
+    <t>현대해상</t>
+  </si>
+  <si>
+    <t>정상 4건</t>
+  </si>
+  <si>
+    <t>총 4건</t>
+  </si>
+  <si>
+    <t>펀드</t>
+  </si>
+  <si>
+    <t>한국투자증권</t>
+  </si>
+  <si>
+    <t>토스증권</t>
+  </si>
+  <si>
+    <t>총 8개</t>
+  </si>
+  <si>
+    <t>기타은행</t>
+  </si>
+  <si>
+    <t>우리은행</t>
+  </si>
+  <si>
+    <t>입출금통장1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>입출금통장3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>입출금통장2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>씨티원예금</t>
-  </si>
-  <si>
-    <t>우리직장인재테크 저축예금(수수료우대형</t>
-  </si>
-  <si>
-    <t>자립예탁금</t>
-  </si>
-  <si>
-    <t>저축예금</t>
-  </si>
-  <si>
-    <t>토스뱅크 통장</t>
-  </si>
-  <si>
-    <t>하나멤버스 주거래통장</t>
-  </si>
-  <si>
-    <t>네이버페이 머니 - bis0****</t>
-  </si>
-  <si>
-    <t>카카오페이 머니 - 010*****187</t>
-  </si>
-  <si>
-    <t>페이코포인트 - bi*****@naver.com</t>
-  </si>
-  <si>
-    <t>미래에셋전략배분TDF솔루션혼합자산자투자신탁C-Pe</t>
-  </si>
-  <si>
-    <t>한국신종개인용MMF3호_C-P</t>
-  </si>
-  <si>
-    <t>한국전력</t>
-  </si>
-  <si>
-    <t>퀀텀 컴퓨팅</t>
-  </si>
-  <si>
-    <t>메타</t>
-  </si>
-  <si>
-    <t>팔란티어</t>
-  </si>
-  <si>
-    <t>금융상품</t>
-  </si>
-  <si>
-    <t>밸런스 CMA</t>
-  </si>
-  <si>
-    <t>연금저축</t>
-  </si>
-  <si>
-    <t>위탁계좌</t>
-  </si>
-  <si>
-    <t>종합</t>
-  </si>
-  <si>
-    <t>종합투자상품</t>
-  </si>
-  <si>
-    <t>보증금</t>
-  </si>
-  <si>
-    <t>무배당 삼성 올라이프 보장보험(0710.5)</t>
-  </si>
-  <si>
-    <t>무배당 삼성화재 통합보험 수퍼플러스(1202)라이프+</t>
-  </si>
-  <si>
-    <t>무배당굿앤굿어린이종합보험Q(Hi2309)1종(표준형)기본플랜</t>
-  </si>
-  <si>
-    <t>무배당실손의료비보장보험(갱신형)(Hi2307)기본플랜</t>
-  </si>
-  <si>
-    <t>현대해상</t>
-  </si>
-  <si>
-    <t>정상 4건</t>
-  </si>
-  <si>
-    <t>총 4건</t>
-  </si>
-  <si>
-    <t>펀드</t>
-  </si>
-  <si>
-    <t>한국투자증권</t>
-  </si>
-  <si>
-    <t>토스증권</t>
-  </si>
-  <si>
-    <t>총 8개</t>
-  </si>
-  <si>
-    <t>기타은행</t>
-  </si>
-  <si>
-    <t>우리은행</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>입출금통장4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>종합1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>종합2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>자립예탁금1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>자립예탁금2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>저축예금1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>저축예금2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -766,7 +798,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -859,10 +891,20 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -872,14 +914,7 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -888,18 +923,16 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1258,747 +1291,745 @@
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="41"/>
+      <c r="D5" s="40"/>
       <c r="E5" s="6">
         <v>36092</v>
       </c>
-      <c r="F5" s="54" t="s">
+      <c r="F5" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="H5" s="41"/>
+      <c r="H5" s="40"/>
       <c r="I5" s="8">
         <v>47471370</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="40"/>
-      <c r="C6" s="41" t="s">
+      <c r="B6" s="41"/>
+      <c r="C6" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="41"/>
+      <c r="D6" s="40"/>
       <c r="E6" s="6">
         <v>5</v>
       </c>
-      <c r="F6" s="54"/>
-      <c r="G6" s="41" t="s">
+      <c r="F6" s="42"/>
+      <c r="G6" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="H6" s="41"/>
+      <c r="H6" s="40"/>
       <c r="I6" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="40"/>
-      <c r="C7" s="41" t="s">
+      <c r="B7" s="41"/>
+      <c r="C7" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="D7" s="41"/>
+      <c r="D7" s="40"/>
       <c r="E7" s="6">
         <v>9</v>
       </c>
       <c r="F7" s="34"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
       <c r="I7" s="9"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="40"/>
-      <c r="C8" s="41" t="s">
+      <c r="B8" s="41"/>
+      <c r="C8" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="41"/>
+      <c r="D8" s="40"/>
       <c r="E8" s="6">
         <v>1844</v>
       </c>
       <c r="F8" s="34"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
       <c r="I8" s="9"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="40"/>
-      <c r="C9" s="41" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" s="41"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="40"/>
       <c r="E9" s="6">
         <v>0</v>
       </c>
       <c r="F9" s="34"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
       <c r="I9" s="9"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="40"/>
-      <c r="C10" s="41" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" s="41"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="40"/>
       <c r="E10" s="6">
         <v>2170345</v>
       </c>
       <c r="F10" s="34"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
       <c r="I10" s="9"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="40"/>
-      <c r="C11" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="41"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="D11" s="40"/>
       <c r="E11" s="6">
         <v>549</v>
       </c>
       <c r="F11" s="34"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
       <c r="I11" s="9"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="40"/>
-      <c r="C12" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="41"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="D12" s="40"/>
       <c r="E12" s="6">
         <v>1557980</v>
       </c>
       <c r="F12" s="34"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
       <c r="I12" s="9"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="40"/>
-      <c r="C13" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="41"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="40"/>
       <c r="E13" s="6">
         <v>1009396</v>
       </c>
       <c r="F13" s="34"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
       <c r="I13" s="9"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="40"/>
-      <c r="C14" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="41"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" s="40"/>
       <c r="E14" s="6">
         <v>2259542</v>
       </c>
       <c r="F14" s="34"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
       <c r="I14" s="9"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="40"/>
-      <c r="C15" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="D15" s="41"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="D15" s="40"/>
       <c r="E15" s="6">
         <v>0</v>
       </c>
       <c r="F15" s="34"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
       <c r="I15" s="9"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="40"/>
-      <c r="C16" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16" s="41"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" s="40"/>
       <c r="E16" s="6">
         <v>4</v>
       </c>
       <c r="F16" s="34"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
       <c r="I16" s="9"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="40"/>
-      <c r="C17" s="41" t="s">
+      <c r="B17" s="41"/>
+      <c r="C17" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="41"/>
+      <c r="D17" s="40"/>
       <c r="E17" s="6">
         <v>100327</v>
       </c>
       <c r="F17" s="34"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
       <c r="I17" s="9"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="40"/>
-      <c r="C18" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" s="41"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="40"/>
       <c r="E18" s="6">
         <v>4960</v>
       </c>
       <c r="F18" s="34"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
       <c r="I18" s="9"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="40"/>
-      <c r="C19" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" s="41"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" s="40"/>
       <c r="E19" s="6">
         <v>3971537</v>
       </c>
       <c r="F19" s="34"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
       <c r="I19" s="9"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="40"/>
-      <c r="C20" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="D20" s="41"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="D20" s="40"/>
       <c r="E20" s="6">
         <v>387417</v>
       </c>
       <c r="F20" s="34"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
       <c r="I20" s="9"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B21" s="40"/>
-      <c r="C21" s="41" t="s">
-        <v>106</v>
-      </c>
-      <c r="D21" s="41"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="40"/>
       <c r="E21" s="6">
         <v>313</v>
       </c>
       <c r="F21" s="34"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
       <c r="I21" s="9"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
       <c r="E22" s="6"/>
       <c r="F22" s="34"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
       <c r="I22" s="9"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="C23" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="41"/>
+      <c r="D23" s="40"/>
       <c r="E23" s="6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="F23" s="34"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
       <c r="I23" s="9"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
       <c r="E24" s="6"/>
       <c r="F24" s="34"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
       <c r="I24" s="9"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="41" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" s="41"/>
+      <c r="C25" s="40" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" s="40"/>
       <c r="E25" s="6">
         <v>0</v>
       </c>
       <c r="F25" s="34"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="40"/>
       <c r="I25" s="9"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B26" s="40"/>
-      <c r="C26" s="41" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" s="41"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="40"/>
       <c r="E26" s="6">
         <v>38720</v>
       </c>
       <c r="F26" s="34"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
       <c r="I26" s="9"/>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B27" s="40"/>
-      <c r="C27" s="41" t="s">
+      <c r="B27" s="41"/>
+      <c r="C27" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="D27" s="41"/>
+      <c r="D27" s="40"/>
       <c r="E27" s="6">
         <v>0</v>
       </c>
       <c r="F27" s="34"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
       <c r="I27" s="9"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B28" s="40"/>
-      <c r="C28" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="41"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="40" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="40"/>
       <c r="E28" s="6">
         <v>5945</v>
       </c>
       <c r="F28" s="34"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
       <c r="I28" s="9"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B29" s="40" t="s">
+      <c r="B29" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="D29" s="41"/>
+      <c r="C29" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" s="40"/>
       <c r="E29" s="6">
         <v>2702374</v>
       </c>
       <c r="F29" s="34"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="41"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
       <c r="I29" s="9"/>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B30" s="40"/>
-      <c r="C30" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="D30" s="41"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="40"/>
       <c r="E30" s="6">
         <v>1156893</v>
       </c>
       <c r="F30" s="34"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
       <c r="I30" s="9"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B31" s="40"/>
-      <c r="C31" s="41" t="s">
+      <c r="B31" s="41"/>
+      <c r="C31" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="41"/>
+      <c r="D31" s="40"/>
       <c r="E31" s="6">
         <v>1950200</v>
       </c>
       <c r="F31" s="34"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
       <c r="I31" s="9"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B32" s="40"/>
-      <c r="C32" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="D32" s="41"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="D32" s="40"/>
       <c r="E32" s="6">
         <v>170250</v>
       </c>
       <c r="F32" s="34"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="41"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="40"/>
       <c r="I32" s="9"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B33" s="40"/>
-      <c r="C33" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="D33" s="41"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" s="40"/>
       <c r="E33" s="6">
         <v>491311.95986152801</v>
       </c>
       <c r="F33" s="34"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="40"/>
       <c r="I33" s="9"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B34" s="40"/>
-      <c r="C34" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="D34" s="41"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="40"/>
       <c r="E34" s="6">
         <v>302954.55181050958</v>
       </c>
       <c r="F34" s="34"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="41"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
       <c r="I34" s="9"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B35" s="40"/>
-      <c r="C35" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="D35" s="41"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="D35" s="40"/>
       <c r="E35" s="6">
         <v>230532.45771932101</v>
       </c>
       <c r="F35" s="34"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="41"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
       <c r="I35" s="9"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B36" s="40"/>
-      <c r="C36" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="D36" s="41"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="D36" s="40"/>
       <c r="E36" s="6">
         <v>170250</v>
       </c>
       <c r="F36" s="34"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="41"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="40"/>
       <c r="I36" s="9"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B37" s="40"/>
-      <c r="C37" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="D37" s="41"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" s="40"/>
       <c r="E37" s="6">
         <v>7118</v>
       </c>
       <c r="F37" s="34"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="41"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="40"/>
       <c r="I37" s="9"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B38" s="40"/>
-      <c r="C38" s="41" t="s">
+      <c r="B38" s="41"/>
+      <c r="C38" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="D38" s="41"/>
+      <c r="D38" s="40"/>
       <c r="E38" s="6">
         <v>502.54610000000002</v>
       </c>
       <c r="F38" s="34"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="41"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="40"/>
       <c r="I38" s="9"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="40"/>
-      <c r="C39" s="41" t="s">
-        <v>117</v>
-      </c>
-      <c r="D39" s="41"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="D39" s="40"/>
       <c r="E39" s="6">
         <v>0</v>
       </c>
       <c r="F39" s="34"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="41"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="40"/>
       <c r="I39" s="9"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="40"/>
-      <c r="C40" s="41" t="s">
-        <v>118</v>
-      </c>
-      <c r="D40" s="41"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="D40" s="40"/>
       <c r="E40" s="6">
         <v>2180772</v>
       </c>
       <c r="F40" s="34"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="41"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
       <c r="I40" s="9"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B41" s="40"/>
-      <c r="C41" s="41" t="s">
-        <v>119</v>
-      </c>
-      <c r="D41" s="41"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="D41" s="40"/>
       <c r="E41" s="6">
         <v>1155453.8015999999</v>
       </c>
       <c r="F41" s="34"/>
-      <c r="G41" s="41"/>
-      <c r="H41" s="41"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
       <c r="I41" s="9"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B42" s="40"/>
-      <c r="C42" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="D42" s="41"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="D42" s="40"/>
       <c r="E42" s="6">
         <v>2</v>
       </c>
       <c r="F42" s="34"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="41"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="40"/>
       <c r="I42" s="9"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B43" s="40"/>
-      <c r="C43" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="D43" s="41"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="D43" s="40"/>
       <c r="E43" s="6">
         <v>2</v>
       </c>
       <c r="F43" s="34"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="41"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="40"/>
       <c r="I43" s="9"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B44" s="40"/>
-      <c r="C44" s="41" t="s">
+      <c r="B44" s="41"/>
+      <c r="C44" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="D44" s="41"/>
+      <c r="D44" s="40"/>
       <c r="E44" s="6">
         <v>4</v>
       </c>
       <c r="F44" s="34"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="41"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="40"/>
       <c r="I44" s="9"/>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B45" s="40"/>
-      <c r="C45" s="41" t="s">
-        <v>121</v>
-      </c>
-      <c r="D45" s="41"/>
+      <c r="B45" s="41"/>
+      <c r="C45" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="D45" s="40"/>
       <c r="E45" s="6">
         <v>24</v>
       </c>
       <c r="F45" s="34"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="41"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="40"/>
       <c r="I45" s="9"/>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="C46" s="41"/>
-      <c r="D46" s="41"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="40"/>
       <c r="E46" s="6"/>
       <c r="F46" s="34"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="41"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="40"/>
       <c r="I46" s="9"/>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="C47" s="41"/>
-      <c r="D47" s="41"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="40"/>
       <c r="E47" s="6"/>
       <c r="F47" s="34"/>
-      <c r="G47" s="41"/>
-      <c r="H47" s="41"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="40"/>
       <c r="I47" s="9"/>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="41" t="s">
-        <v>122</v>
-      </c>
-      <c r="D48" s="41"/>
-      <c r="E48" s="6">
-        <v>42000000</v>
-      </c>
+      <c r="C48" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="D48" s="40"/>
+      <c r="E48" s="6"/>
       <c r="F48" s="34"/>
-      <c r="G48" s="41"/>
-      <c r="H48" s="41"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="40"/>
       <c r="I48" s="9"/>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B49" s="40" t="s">
+      <c r="B49" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="C49" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="D49" s="41"/>
+      <c r="C49" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="D49" s="40"/>
       <c r="E49" s="6">
         <v>0</v>
       </c>
       <c r="F49" s="34"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="41"/>
+      <c r="G49" s="40"/>
+      <c r="H49" s="40"/>
       <c r="I49" s="9"/>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B50" s="40"/>
-      <c r="C50" s="41" t="s">
-        <v>124</v>
-      </c>
-      <c r="D50" s="41"/>
+      <c r="B50" s="41"/>
+      <c r="C50" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="D50" s="40"/>
       <c r="E50" s="6">
         <v>0</v>
       </c>
       <c r="F50" s="34"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="41"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="40"/>
       <c r="I50" s="9"/>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B51" s="40"/>
-      <c r="C51" s="41" t="s">
-        <v>125</v>
-      </c>
-      <c r="D51" s="41"/>
+      <c r="B51" s="41"/>
+      <c r="C51" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="D51" s="40"/>
       <c r="E51" s="6">
         <v>0</v>
       </c>
       <c r="F51" s="34"/>
-      <c r="G51" s="41"/>
-      <c r="H51" s="41"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="40"/>
       <c r="I51" s="9"/>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B52" s="40"/>
-      <c r="C52" s="41" t="s">
-        <v>126</v>
-      </c>
-      <c r="D52" s="41"/>
+      <c r="B52" s="41"/>
+      <c r="C52" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="D52" s="40"/>
       <c r="E52" s="6">
         <v>0</v>
       </c>
       <c r="F52" s="34"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="41"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="40"/>
       <c r="I52" s="9"/>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="C53" s="41"/>
-      <c r="D53" s="41"/>
+      <c r="C53" s="40"/>
+      <c r="D53" s="40"/>
       <c r="E53" s="6"/>
       <c r="F53" s="34"/>
-      <c r="G53" s="41"/>
-      <c r="H53" s="41"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="40"/>
       <c r="I53" s="9"/>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B54" s="42" t="s">
+      <c r="B54" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="C54" s="42"/>
-      <c r="D54" s="42"/>
+      <c r="C54" s="46"/>
+      <c r="D54" s="46"/>
       <c r="E54" s="10">
         <f>SUM(E5:E53)</f>
-        <v>65063629.317091361</v>
-      </c>
-      <c r="F54" s="43" t="s">
+        <v>22063629.317091361</v>
+      </c>
+      <c r="F54" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="G54" s="43"/>
-      <c r="H54" s="43"/>
+      <c r="G54" s="47"/>
+      <c r="H54" s="47"/>
       <c r="I54" s="11">
         <f>SUM(I5:I53)</f>
         <v>47471370</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B55" s="44" t="s">
+      <c r="B55" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="C55" s="44"/>
-      <c r="D55" s="44"/>
-      <c r="E55" s="44"/>
-      <c r="F55" s="44"/>
-      <c r="G55" s="44"/>
-      <c r="H55" s="44"/>
-      <c r="I55" s="44"/>
+      <c r="C55" s="48"/>
+      <c r="D55" s="48"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="48"/>
+      <c r="H55" s="48"/>
+      <c r="I55" s="48"/>
     </row>
     <row r="56" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="45">
+      <c r="B56" s="43">
         <f>E54-I54</f>
-        <v>17592259.317091361</v>
-      </c>
-      <c r="C56" s="45"/>
-      <c r="D56" s="45"/>
-      <c r="E56" s="45"/>
-      <c r="F56" s="45"/>
-      <c r="G56" s="45"/>
-      <c r="H56" s="45"/>
-      <c r="I56" s="45"/>
+        <v>-25407740.682908639</v>
+      </c>
+      <c r="C56" s="43"/>
+      <c r="D56" s="43"/>
+      <c r="E56" s="43"/>
+      <c r="F56" s="43"/>
+      <c r="G56" s="43"/>
+      <c r="H56" s="43"/>
+      <c r="I56" s="43"/>
     </row>
     <row r="59" spans="2:9" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
@@ -2014,10 +2045,10 @@
       <c r="B61" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C61" s="46" t="s">
+      <c r="C61" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="D61" s="46"/>
+      <c r="D61" s="44"/>
       <c r="E61" s="33" t="s">
         <v>56</v>
       </c>
@@ -2035,10 +2066,10 @@
       <c r="B62" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C62" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="D62" s="47"/>
+      <c r="C62" s="45" t="s">
+        <v>119</v>
+      </c>
+      <c r="D62" s="45"/>
       <c r="E62" s="16" t="s">
         <v>61</v>
       </c>
@@ -2056,10 +2087,10 @@
       <c r="B63" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="47" t="s">
-        <v>124</v>
-      </c>
-      <c r="D63" s="47"/>
+      <c r="C63" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="D63" s="45"/>
       <c r="E63" s="16" t="s">
         <v>61</v>
       </c>
@@ -2075,12 +2106,12 @@
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="C64" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="D64" s="47"/>
+        <v>123</v>
+      </c>
+      <c r="C64" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="D64" s="45"/>
       <c r="E64" s="16" t="s">
         <v>61</v>
       </c>
@@ -2096,12 +2127,12 @@
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B65" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="C65" s="47" t="s">
-        <v>126</v>
-      </c>
-      <c r="D65" s="47"/>
+        <v>123</v>
+      </c>
+      <c r="C65" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="D65" s="45"/>
       <c r="E65" s="16" t="s">
         <v>61</v>
       </c>
@@ -2116,15 +2147,15 @@
       </c>
     </row>
     <row r="66" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="53" t="s">
+      <c r="B66" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C66" s="49" t="s">
+      <c r="C66" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="D66" s="49"/>
+      <c r="D66" s="50"/>
       <c r="E66" s="28" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F66" s="28" t="s">
         <v>65</v>
@@ -2133,11 +2164,11 @@
       <c r="H66" s="20"/>
     </row>
     <row r="67" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="53"/>
-      <c r="C67" s="50" t="s">
-        <v>129</v>
-      </c>
-      <c r="D67" s="50"/>
+      <c r="B67" s="49"/>
+      <c r="C67" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="D67" s="51"/>
       <c r="E67" s="29" t="s">
         <v>67</v>
       </c>
@@ -2165,10 +2196,10 @@
       <c r="C71" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="D71" s="46" t="s">
+      <c r="D71" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="E71" s="46"/>
+      <c r="E71" s="44"/>
       <c r="F71" s="33" t="s">
         <v>71</v>
       </c>
@@ -2187,15 +2218,15 @@
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B72" s="14" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C72" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="D72" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="E72" s="47"/>
+        <v>127</v>
+      </c>
+      <c r="D72" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="E72" s="45"/>
       <c r="F72" s="17">
         <v>1946016</v>
       </c>
@@ -2210,15 +2241,15 @@
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B73" s="14" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C73" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="D73" s="47" t="s">
-        <v>111</v>
-      </c>
-      <c r="E73" s="47"/>
+        <v>127</v>
+      </c>
+      <c r="D73" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="E73" s="45"/>
       <c r="F73" s="17">
         <v>1000001</v>
       </c>
@@ -2236,12 +2267,12 @@
         <v>75</v>
       </c>
       <c r="C74" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="D74" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="D74" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="E74" s="47"/>
+      <c r="E74" s="45"/>
       <c r="F74" s="17">
         <v>1831849</v>
       </c>
@@ -2259,12 +2290,12 @@
         <v>75</v>
       </c>
       <c r="C75" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="D75" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="E75" s="47"/>
+        <v>127</v>
+      </c>
+      <c r="D75" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="E75" s="45"/>
       <c r="F75" s="17">
         <v>143500</v>
       </c>
@@ -2282,12 +2313,12 @@
         <v>75</v>
       </c>
       <c r="C76" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="D76" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="E76" s="47"/>
+        <v>128</v>
+      </c>
+      <c r="D76" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="E76" s="45"/>
       <c r="F76" s="17">
         <v>1064609</v>
       </c>
@@ -2305,12 +2336,12 @@
         <v>75</v>
       </c>
       <c r="C77" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="D77" s="47" t="s">
-        <v>114</v>
-      </c>
-      <c r="E77" s="47"/>
+        <v>128</v>
+      </c>
+      <c r="D77" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="E77" s="45"/>
       <c r="F77" s="17">
         <v>297847</v>
       </c>
@@ -2328,12 +2359,12 @@
         <v>75</v>
       </c>
       <c r="C78" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="D78" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="E78" s="47"/>
+        <v>128</v>
+      </c>
+      <c r="D78" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="E78" s="45"/>
       <c r="F78" s="17">
         <v>296496</v>
       </c>
@@ -2351,12 +2382,12 @@
         <v>75</v>
       </c>
       <c r="C79" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="D79" s="47" t="s">
-        <v>112</v>
-      </c>
-      <c r="E79" s="47"/>
+        <v>128</v>
+      </c>
+      <c r="D79" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="E79" s="45"/>
       <c r="F79" s="17">
         <v>296500</v>
       </c>
@@ -2370,14 +2401,14 @@
       <c r="J79" s="18"/>
     </row>
     <row r="80" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="48" t="s">
+      <c r="B80" s="52" t="s">
         <v>1</v>
       </c>
       <c r="C80" s="28"/>
-      <c r="D80" s="49" t="s">
+      <c r="D80" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="E80" s="49"/>
+      <c r="E80" s="50"/>
       <c r="F80" s="28" t="s">
         <v>78</v>
       </c>
@@ -2391,12 +2422,12 @@
       <c r="J80" s="20"/>
     </row>
     <row r="81" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="48"/>
+      <c r="B81" s="52"/>
       <c r="C81" s="29"/>
-      <c r="D81" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="E81" s="50"/>
+      <c r="D81" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="E81" s="51"/>
       <c r="F81" s="32">
         <f>SUM(F72:F79)</f>
         <v>6876818</v>
@@ -2429,10 +2460,10 @@
       <c r="C85" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D85" s="51" t="s">
+      <c r="D85" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="E85" s="51"/>
+      <c r="E85" s="54"/>
       <c r="F85" s="30" t="s">
         <v>85</v>
       </c>
@@ -2454,12 +2485,12 @@
         <v>90</v>
       </c>
       <c r="C86" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="D86" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="D86" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="E86" s="47"/>
+      <c r="E86" s="45"/>
       <c r="F86" s="17">
         <v>0</v>
       </c>
@@ -2479,12 +2510,12 @@
         <v>90</v>
       </c>
       <c r="C87" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="D87" s="47" t="s">
+        <v>131</v>
+      </c>
+      <c r="D87" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="E87" s="47"/>
+      <c r="E87" s="45"/>
       <c r="F87" s="17">
         <v>40000000</v>
       </c>
@@ -2502,14 +2533,14 @@
       </c>
     </row>
     <row r="88" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="48" t="s">
+      <c r="B88" s="52" t="s">
         <v>1</v>
       </c>
       <c r="C88" s="28"/>
-      <c r="D88" s="49" t="s">
+      <c r="D88" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="E88" s="49"/>
+      <c r="E88" s="50"/>
       <c r="F88" s="28" t="s">
         <v>93</v>
       </c>
@@ -2521,13 +2552,13 @@
       <c r="J88" s="20"/>
     </row>
     <row r="89" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B89" s="48"/>
+      <c r="B89" s="52"/>
       <c r="C89" s="29"/>
-      <c r="D89" s="52">
+      <c r="D89" s="53">
         <f>SUM(2)</f>
         <v>2</v>
       </c>
-      <c r="E89" s="52"/>
+      <c r="E89" s="53"/>
       <c r="F89" s="32">
         <f>SUM(F86:F87)</f>
         <v>40000000</v>
@@ -2585,6 +2616,10 @@
     <mergeCell ref="C51:D51"/>
     <mergeCell ref="G51:H51"/>
     <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="G38:H38"/>
     <mergeCell ref="C45:D45"/>
     <mergeCell ref="G45:H45"/>
     <mergeCell ref="C46:D46"/>
@@ -2597,18 +2632,6 @@
     <mergeCell ref="G43:H43"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="G44:H44"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="G38:H38"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="C34:D34"/>
@@ -2625,6 +2648,14 @@
     <mergeCell ref="G31:H31"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="G32:H32"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="G36:H36"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="B25:B28"/>
@@ -2635,8 +2666,6 @@
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="G27:H27"/>
     <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="G21:H21"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="G22:H22"/>
     <mergeCell ref="C23:D23"/>
@@ -2647,10 +2676,6 @@
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="G20:H20"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="G16:H16"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="C12:D12"/>
@@ -2659,6 +2684,12 @@
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="G14:H14"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G4:H4"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="C10:D10"/>
@@ -2675,10 +2706,10 @@
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="G16:H16"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2688,24 +2719,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J68"/>
+  <dimension ref="B1:L68"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.75" customWidth="1"/>
     <col min="2" max="18" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:12" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="37" t="s">
         <v>4</v>
       </c>
@@ -2719,7 +2750,7 @@
       <c r="H3" s="38"/>
       <c r="I3" s="38"/>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>0</v>
       </c>
@@ -2741,534 +2772,542 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="40" t="s">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="41"/>
+      <c r="D5" s="40"/>
       <c r="E5" s="6">
         <v>3931685</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="H5" s="41"/>
+      <c r="H5" s="40"/>
       <c r="I5" s="8">
         <v>600000000</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="40"/>
-      <c r="C6" s="41" t="s">
+      <c r="K5" s="55">
+        <f>SUM(E5:E14)+100000</f>
+        <v>26891042</v>
+      </c>
+      <c r="L5" s="55">
+        <f>SUM('뱅샐현황(재은)'!E5:E21)</f>
+        <v>11500320</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="41"/>
+      <c r="C6" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="41"/>
+      <c r="D6" s="40"/>
       <c r="E6" s="6">
         <v>13090630</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="40"/>
-      <c r="C7" s="41" t="s">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="41"/>
+      <c r="C7" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="41"/>
+      <c r="D7" s="40"/>
       <c r="E7" s="6">
         <v>41</v>
       </c>
       <c r="F7" s="5"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="40"/>
-      <c r="C8" s="41" t="s">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="41"/>
+      <c r="C8" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="41"/>
+      <c r="D8" s="40"/>
       <c r="E8" s="6">
         <v>2</v>
       </c>
       <c r="F8" s="5"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="40"/>
-      <c r="C9" s="41" t="s">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="41"/>
+      <c r="C9" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="41"/>
+      <c r="D9" s="40"/>
       <c r="E9" s="6">
         <v>3269297</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="40"/>
-      <c r="C10" s="41" t="s">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="41"/>
+      <c r="C10" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="41"/>
+      <c r="D10" s="40"/>
       <c r="E10" s="6">
         <v>1107</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="40"/>
-      <c r="C11" s="41" t="s">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="41"/>
+      <c r="C11" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="41"/>
+      <c r="D11" s="40"/>
       <c r="E11" s="6">
         <v>126</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="40"/>
-      <c r="C12" s="41" t="s">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="41"/>
+      <c r="C12" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="41"/>
+      <c r="D12" s="40"/>
       <c r="E12" s="6">
         <v>6449648</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="40"/>
-      <c r="C13" s="41" t="s">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="41"/>
+      <c r="C13" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="41"/>
+      <c r="D13" s="40"/>
       <c r="E13" s="6">
         <v>7000</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="40"/>
-      <c r="C14" s="41" t="s">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="41"/>
+      <c r="C14" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="41"/>
+      <c r="D14" s="40"/>
       <c r="E14" s="6">
         <v>41506</v>
       </c>
       <c r="F14" s="5"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
       <c r="E15" s="6"/>
       <c r="F15" s="5"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="41"/>
+      <c r="D16" s="40"/>
       <c r="E16" s="6">
         <v>0</v>
       </c>
       <c r="F16" s="5"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
       <c r="I16" s="9"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="C17" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="41"/>
+      <c r="D17" s="40"/>
       <c r="E17" s="6">
         <v>100000</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
       <c r="I17" s="9"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="41"/>
+      <c r="D18" s="40"/>
       <c r="E18" s="6">
         <v>0</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
       <c r="I18" s="9"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="40"/>
-      <c r="C19" s="41" t="s">
+      <c r="B19" s="41"/>
+      <c r="C19" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="41"/>
+      <c r="D19" s="40"/>
       <c r="E19" s="6">
         <v>0</v>
       </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
       <c r="I19" s="9"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="40"/>
-      <c r="C20" s="41" t="s">
+      <c r="B20" s="41"/>
+      <c r="C20" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="41"/>
+      <c r="D20" s="40"/>
       <c r="E20" s="6">
         <v>12000</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
       <c r="I20" s="9"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B21" s="40"/>
-      <c r="C21" s="41" t="s">
+      <c r="B21" s="41"/>
+      <c r="C21" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="41"/>
+      <c r="D21" s="40"/>
       <c r="E21" s="6">
         <v>0</v>
       </c>
       <c r="F21" s="5"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
       <c r="I21" s="9"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B22" s="40" t="s">
+      <c r="B22" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="41"/>
+      <c r="D22" s="40"/>
       <c r="E22" s="6">
         <v>1919980</v>
       </c>
       <c r="F22" s="5"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
       <c r="I22" s="9"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="40"/>
-      <c r="C23" s="41" t="s">
+      <c r="B23" s="41"/>
+      <c r="C23" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="41"/>
+      <c r="D23" s="40"/>
       <c r="E23" s="6">
         <v>1726080</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
       <c r="I23" s="9"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B24" s="40"/>
-      <c r="C24" s="41" t="s">
+      <c r="B24" s="41"/>
+      <c r="C24" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="41"/>
+      <c r="D24" s="40"/>
       <c r="E24" s="6">
         <v>20105</v>
       </c>
       <c r="F24" s="5"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
       <c r="I24" s="9"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B25" s="40"/>
-      <c r="C25" s="41" t="s">
+      <c r="B25" s="41"/>
+      <c r="C25" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="41"/>
+      <c r="D25" s="40"/>
       <c r="E25" s="6">
         <v>446955.17499999999</v>
       </c>
       <c r="F25" s="5"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="40"/>
       <c r="I25" s="9"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B26" s="40"/>
-      <c r="C26" s="41" t="s">
+      <c r="B26" s="41"/>
+      <c r="C26" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="D26" s="41"/>
+      <c r="D26" s="40"/>
       <c r="E26" s="6">
         <v>3481.8249999999998</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
       <c r="I26" s="9"/>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B27" s="40"/>
-      <c r="C27" s="41" t="s">
+      <c r="B27" s="41"/>
+      <c r="C27" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="41"/>
+      <c r="D27" s="40"/>
       <c r="E27" s="6">
         <v>282</v>
       </c>
       <c r="F27" s="5"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
       <c r="I27" s="9"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B28" s="40"/>
-      <c r="C28" s="41" t="s">
+      <c r="B28" s="41"/>
+      <c r="C28" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="D28" s="41"/>
+      <c r="D28" s="40"/>
       <c r="E28" s="6">
         <v>693121</v>
       </c>
       <c r="F28" s="5"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
       <c r="I28" s="9"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B29" s="40"/>
-      <c r="C29" s="41" t="s">
+      <c r="B29" s="41"/>
+      <c r="C29" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="41"/>
+      <c r="D29" s="40"/>
       <c r="E29" s="6">
         <v>1</v>
       </c>
       <c r="F29" s="5"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="41"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
       <c r="I29" s="9"/>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
       <c r="E30" s="6"/>
       <c r="F30" s="5"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
       <c r="I30" s="9"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
       <c r="E31" s="6"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
       <c r="I31" s="9"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
       <c r="E32" s="6"/>
       <c r="F32" s="5"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="41"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="40"/>
       <c r="I32" s="9"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B33" s="40" t="s">
+      <c r="B33" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="41" t="s">
+      <c r="C33" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="D33" s="41"/>
+      <c r="D33" s="40"/>
       <c r="E33" s="6">
         <v>0</v>
       </c>
       <c r="F33" s="5"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="40"/>
       <c r="I33" s="9"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B34" s="40"/>
-      <c r="C34" s="41" t="s">
+      <c r="B34" s="41"/>
+      <c r="C34" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="D34" s="41"/>
+      <c r="D34" s="40"/>
       <c r="E34" s="6">
         <v>0</v>
       </c>
       <c r="F34" s="5"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="41"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
       <c r="I34" s="9"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B35" s="40"/>
-      <c r="C35" s="41" t="s">
+      <c r="B35" s="41"/>
+      <c r="C35" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="D35" s="41"/>
+      <c r="D35" s="40"/>
       <c r="E35" s="6">
         <v>0</v>
       </c>
       <c r="F35" s="5"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="41"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
       <c r="I35" s="9"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B36" s="40"/>
-      <c r="C36" s="41" t="s">
+      <c r="B36" s="41"/>
+      <c r="C36" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="D36" s="41"/>
+      <c r="D36" s="40"/>
       <c r="E36" s="6">
         <v>0</v>
       </c>
       <c r="F36" s="5"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="41"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="40"/>
       <c r="I36" s="9"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B37" s="40"/>
-      <c r="C37" s="41" t="s">
+      <c r="B37" s="41"/>
+      <c r="C37" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="D37" s="41"/>
+      <c r="D37" s="40"/>
       <c r="E37" s="6">
         <v>0</v>
       </c>
       <c r="F37" s="5"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="41"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="40"/>
       <c r="I37" s="9"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
       <c r="E38" s="6"/>
       <c r="F38" s="5"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="41"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="40"/>
       <c r="I38" s="9"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="42" t="s">
+      <c r="B39" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="C39" s="42"/>
-      <c r="D39" s="42"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46"/>
       <c r="E39" s="10">
         <f>SUM(E5:E38)</f>
         <v>31713048</v>
       </c>
-      <c r="F39" s="43" t="s">
+      <c r="F39" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="G39" s="43"/>
-      <c r="H39" s="43"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="47"/>
       <c r="I39" s="11">
         <f>SUM(I5:I38)</f>
         <v>600000000</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="44" t="s">
+      <c r="B40" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="44"/>
-      <c r="D40" s="44"/>
-      <c r="E40" s="44"/>
-      <c r="F40" s="44"/>
-      <c r="G40" s="44"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="44"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48"/>
+      <c r="G40" s="48"/>
+      <c r="H40" s="48"/>
+      <c r="I40" s="48"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B41" s="45">
+      <c r="B41" s="43">
         <f>E39-I39</f>
         <v>-568286952</v>
       </c>
-      <c r="C41" s="45"/>
-      <c r="D41" s="45"/>
-      <c r="E41" s="45"/>
-      <c r="F41" s="45"/>
-      <c r="G41" s="45"/>
-      <c r="H41" s="45"/>
-      <c r="I41" s="45"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
     </row>
     <row r="44" spans="2:9" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
@@ -3284,10 +3323,10 @@
       <c r="B46" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C46" s="46" t="s">
+      <c r="C46" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="D46" s="46"/>
+      <c r="D46" s="44"/>
       <c r="E46" s="13" t="s">
         <v>56</v>
       </c>
@@ -3305,10 +3344,10 @@
       <c r="B47" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C47" s="47" t="s">
+      <c r="C47" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="D47" s="47"/>
+      <c r="D47" s="45"/>
       <c r="E47" s="16" t="s">
         <v>61</v>
       </c>
@@ -3326,10 +3365,10 @@
       <c r="B48" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C48" s="47" t="s">
+      <c r="C48" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="D48" s="47"/>
+      <c r="D48" s="45"/>
       <c r="E48" s="16" t="s">
         <v>61</v>
       </c>
@@ -3347,10 +3386,10 @@
       <c r="B49" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C49" s="47" t="s">
+      <c r="C49" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="D49" s="47"/>
+      <c r="D49" s="45"/>
       <c r="E49" s="16" t="s">
         <v>61</v>
       </c>
@@ -3368,10 +3407,10 @@
       <c r="B50" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C50" s="47" t="s">
+      <c r="C50" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="D50" s="47"/>
+      <c r="D50" s="45"/>
       <c r="E50" s="16" t="s">
         <v>61</v>
       </c>
@@ -3389,10 +3428,10 @@
       <c r="B51" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C51" s="47" t="s">
+      <c r="C51" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="D51" s="47"/>
+      <c r="D51" s="45"/>
       <c r="E51" s="16" t="s">
         <v>61</v>
       </c>
@@ -3407,13 +3446,13 @@
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B52" s="53" t="s">
+      <c r="B52" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C52" s="49" t="s">
+      <c r="C52" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="D52" s="49"/>
+      <c r="D52" s="50"/>
       <c r="E52" s="19" t="s">
         <v>64</v>
       </c>
@@ -3424,11 +3463,11 @@
       <c r="H52" s="20"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B53" s="53"/>
-      <c r="C53" s="50" t="s">
+      <c r="B53" s="49"/>
+      <c r="C53" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="D53" s="50"/>
+      <c r="D53" s="51"/>
       <c r="E53" s="21" t="s">
         <v>67</v>
       </c>
@@ -3456,10 +3495,10 @@
       <c r="C57" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D57" s="46" t="s">
+      <c r="D57" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="E57" s="46"/>
+      <c r="E57" s="44"/>
       <c r="F57" s="13" t="s">
         <v>71</v>
       </c>
@@ -3483,10 +3522,10 @@
       <c r="C58" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="D58" s="47" t="s">
+      <c r="D58" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="E58" s="47"/>
+      <c r="E58" s="45"/>
       <c r="F58" s="17">
         <v>1277189</v>
       </c>
@@ -3506,10 +3545,10 @@
       <c r="C59" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="D59" s="47" t="s">
+      <c r="D59" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="E59" s="47"/>
+      <c r="E59" s="45"/>
       <c r="F59" s="17">
         <v>1737959</v>
       </c>
@@ -3523,14 +3562,14 @@
       <c r="J59" s="18"/>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B60" s="48" t="s">
+      <c r="B60" s="52" t="s">
         <v>1</v>
       </c>
       <c r="C60" s="19"/>
-      <c r="D60" s="49" t="s">
+      <c r="D60" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="E60" s="49"/>
+      <c r="E60" s="50"/>
       <c r="F60" s="19" t="s">
         <v>78</v>
       </c>
@@ -3544,12 +3583,12 @@
       <c r="J60" s="20"/>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B61" s="48"/>
+      <c r="B61" s="52"/>
       <c r="C61" s="21"/>
-      <c r="D61" s="50" t="s">
+      <c r="D61" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="E61" s="50"/>
+      <c r="E61" s="51"/>
       <c r="F61" s="22">
         <f>SUM(F58:F59)</f>
         <v>3015148</v>
@@ -3582,10 +3621,10 @@
       <c r="C65" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="D65" s="51" t="s">
+      <c r="D65" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="E65" s="51"/>
+      <c r="E65" s="54"/>
       <c r="F65" s="27" t="s">
         <v>85</v>
       </c>
@@ -3609,10 +3648,10 @@
       <c r="C66" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D66" s="47" t="s">
+      <c r="D66" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="E66" s="47"/>
+      <c r="E66" s="45"/>
       <c r="F66" s="17">
         <v>600000000</v>
       </c>
@@ -3630,14 +3669,14 @@
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B67" s="48" t="s">
+      <c r="B67" s="52" t="s">
         <v>1</v>
       </c>
       <c r="C67" s="19"/>
-      <c r="D67" s="49" t="s">
+      <c r="D67" s="50" t="s">
         <v>92</v>
       </c>
-      <c r="E67" s="49"/>
+      <c r="E67" s="50"/>
       <c r="F67" s="19" t="s">
         <v>93</v>
       </c>
@@ -3649,13 +3688,13 @@
       <c r="J67" s="20"/>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B68" s="48"/>
+      <c r="B68" s="52"/>
       <c r="C68" s="21"/>
-      <c r="D68" s="52">
+      <c r="D68" s="53">
         <f>SUM(1)</f>
         <v>1</v>
       </c>
-      <c r="E68" s="52"/>
+      <c r="E68" s="53"/>
       <c r="F68" s="22">
         <f>SUM(F66)</f>
         <v>600000000</v>
@@ -3675,10 +3714,6 @@
     <mergeCell ref="B67:B68"/>
     <mergeCell ref="D67:E67"/>
     <mergeCell ref="D68:E68"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C38:D38"/>
     <mergeCell ref="B60:B61"/>
     <mergeCell ref="D60:E60"/>
     <mergeCell ref="D61:E61"/>
@@ -3691,32 +3726,41 @@
     <mergeCell ref="D57:E57"/>
     <mergeCell ref="D58:E58"/>
     <mergeCell ref="D59:E59"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
     <mergeCell ref="G38:H38"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="F39:H39"/>
-    <mergeCell ref="B40:I40"/>
-    <mergeCell ref="B41:I41"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G15:H15"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="G34:H34"/>
     <mergeCell ref="G35:H35"/>
     <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G22:H22"/>
     <mergeCell ref="G37:H37"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="G29:H29"/>
@@ -3732,11 +3776,6 @@
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C37:D37"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
     <mergeCell ref="B22:B29"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C23:D23"/>

--- a/20260713(asset).xlsx
+++ b/20260713(asset).xlsx
@@ -9,18 +9,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="뱅샐현황(재은)" sheetId="2" r:id="rId1"/>
-    <sheet name="뱅샐현황(영범)" sheetId="1" r:id="rId2"/>
+    <sheet name="뱅샐현황" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="146">
   <si>
     <t>항목</t>
   </si>
@@ -28,9 +28,6 @@
     <t>총계</t>
   </si>
   <si>
-    <t>3.재무현황</t>
-  </si>
-  <si>
     <t>데이터를 내보낸 시점의 자산과 부채 상태를 분석합니다.</t>
   </si>
   <si>
@@ -287,9 +284,6 @@
   </si>
   <si>
     <t>대출신규일</t>
-  </si>
-  <si>
-    <t>대출만기일</t>
   </si>
   <si>
     <t>은행 대출</t>
@@ -460,6 +454,26 @@
   </si>
   <si>
     <t>저축예금2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>미래에셋전략배분TDF솔루션혼합자산자투자신탁C-Pe</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>재은</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영범</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>재은</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>영범</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -471,7 +485,7 @@
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="#,##0.00\ &quot;%&quot;\ "/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -508,6 +522,13 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -561,7 +582,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -794,11 +815,113 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -859,9 +982,15 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -869,9 +998,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -882,6 +1008,47 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -891,48 +1058,70 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1237,841 +1426,954 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J89"/>
+  <dimension ref="A1:I157"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.75" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="18" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="65" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1" s="66" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="68"/>
+    </row>
+    <row r="2" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="69"/>
+      <c r="B2" s="70" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="71"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="69"/>
+      <c r="B3" s="53" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="37" t="s">
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="69"/>
       <c r="B4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="55"/>
+      <c r="E4" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="39"/>
-      <c r="E4" s="36" t="s">
+      <c r="F4" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="G4" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="55"/>
+      <c r="I4" s="37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="69"/>
+      <c r="B5" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="G4" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" s="39"/>
-      <c r="I4" s="36" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" s="40"/>
+      <c r="C5" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="49"/>
       <c r="E5" s="6">
         <v>36092</v>
       </c>
-      <c r="F5" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="40" t="s">
-        <v>97</v>
-      </c>
-      <c r="H5" s="40"/>
+      <c r="F5" s="56" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="H5" s="49"/>
       <c r="I5" s="8">
         <v>47471370</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="41"/>
-      <c r="C6" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="40"/>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="69"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="49"/>
       <c r="E6" s="6">
         <v>5</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="H6" s="40"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="H6" s="49"/>
       <c r="I6" s="8">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="41"/>
-      <c r="C7" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="D7" s="40"/>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="69"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="49"/>
       <c r="E7" s="6">
         <v>9</v>
       </c>
-      <c r="F7" s="34"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="41"/>
-      <c r="C8" s="40" t="s">
-        <v>100</v>
-      </c>
-      <c r="D8" s="40"/>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="69"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="49"/>
       <c r="E8" s="6">
         <v>1844</v>
       </c>
-      <c r="F8" s="34"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="41"/>
-      <c r="C9" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="D9" s="40"/>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="69"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" s="49"/>
       <c r="E9" s="6">
         <v>0</v>
       </c>
-      <c r="F9" s="34"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="41"/>
-      <c r="C10" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" s="40"/>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="69"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="49" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="49"/>
       <c r="E10" s="6">
         <v>2170345</v>
       </c>
-      <c r="F10" s="34"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="41"/>
-      <c r="C11" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="D11" s="40"/>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="69"/>
+      <c r="B11" s="52"/>
+      <c r="C11" s="49" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" s="49"/>
       <c r="E11" s="6">
         <v>549</v>
       </c>
-      <c r="F11" s="34"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="41"/>
-      <c r="C12" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="D12" s="40"/>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="69"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="D12" s="49"/>
       <c r="E12" s="6">
         <v>1557980</v>
       </c>
-      <c r="F12" s="34"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="41"/>
-      <c r="C13" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="D13" s="40"/>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="69"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="D13" s="49"/>
       <c r="E13" s="6">
         <v>1009396</v>
       </c>
-      <c r="F13" s="34"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="41"/>
-      <c r="C14" s="40" t="s">
-        <v>136</v>
-      </c>
-      <c r="D14" s="40"/>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="69"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="D14" s="49"/>
       <c r="E14" s="6">
         <v>2259542</v>
       </c>
-      <c r="F14" s="34"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="41"/>
-      <c r="C15" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="D15" s="40"/>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="69"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="49" t="s">
+        <v>137</v>
+      </c>
+      <c r="D15" s="49"/>
       <c r="E15" s="6">
         <v>0</v>
       </c>
-      <c r="F15" s="34"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="41"/>
-      <c r="C16" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="D16" s="40"/>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="69"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="49"/>
       <c r="E16" s="6">
         <v>4</v>
       </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="41"/>
-      <c r="C17" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="40"/>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="69"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="49"/>
       <c r="E17" s="6">
         <v>100327</v>
       </c>
-      <c r="F17" s="34"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="49"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="41"/>
-      <c r="C18" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="D18" s="40"/>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="69"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="D18" s="49"/>
       <c r="E18" s="6">
         <v>4960</v>
       </c>
-      <c r="F18" s="34"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="49"/>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="41"/>
-      <c r="C19" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="D19" s="40"/>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="69"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="D19" s="49"/>
       <c r="E19" s="6">
         <v>3971537</v>
       </c>
-      <c r="F19" s="34"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="49"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="41"/>
-      <c r="C20" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="D20" s="40"/>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="69"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="49"/>
       <c r="E20" s="6">
         <v>387417</v>
       </c>
-      <c r="F20" s="34"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
       <c r="I20" s="9"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B21" s="41"/>
-      <c r="C21" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="D21" s="40"/>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="69"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="49" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="49"/>
       <c r="E21" s="6">
         <v>313</v>
       </c>
-      <c r="F21" s="34"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="49"/>
       <c r="I21" s="9"/>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B22" s="35" t="s">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="69"/>
+      <c r="B22" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="49"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="9"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="69"/>
+      <c r="B23" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="9"/>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="35" t="s">
+      <c r="C23" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="40"/>
+      <c r="D23" s="49"/>
       <c r="E23" s="6">
         <v>0</v>
       </c>
-      <c r="F23" s="34"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B24" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="69"/>
+      <c r="B24" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
       <c r="E24" s="6"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="49"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B25" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" s="40"/>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="69"/>
+      <c r="B25" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="D25" s="49"/>
       <c r="E25" s="6">
         <v>0</v>
       </c>
-      <c r="F25" s="34"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="49"/>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B26" s="41"/>
-      <c r="C26" s="40" t="s">
-        <v>105</v>
-      </c>
-      <c r="D26" s="40"/>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="69"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" s="49"/>
       <c r="E26" s="6">
         <v>38720</v>
       </c>
-      <c r="F26" s="34"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B27" s="41"/>
-      <c r="C27" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27" s="40"/>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="69"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="49"/>
       <c r="E27" s="6">
         <v>0</v>
       </c>
-      <c r="F27" s="34"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="49"/>
       <c r="I27" s="9"/>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B28" s="41"/>
-      <c r="C28" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" s="40"/>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="69"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" s="49"/>
       <c r="E28" s="6">
         <v>5945</v>
       </c>
-      <c r="F28" s="34"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="49"/>
       <c r="I28" s="9"/>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B29" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" s="40"/>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="69"/>
+      <c r="B29" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="49" t="s">
+        <v>141</v>
+      </c>
+      <c r="D29" s="49"/>
       <c r="E29" s="6">
         <v>2702374</v>
       </c>
-      <c r="F29" s="34"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="40"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="49"/>
       <c r="I29" s="9"/>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B30" s="41"/>
-      <c r="C30" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="D30" s="40"/>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="69"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="D30" s="49"/>
       <c r="E30" s="6">
         <v>1156893</v>
       </c>
-      <c r="F30" s="34"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="49"/>
+      <c r="H30" s="49"/>
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B31" s="41"/>
-      <c r="C31" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31" s="40"/>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="69"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="49"/>
       <c r="E31" s="6">
         <v>1950200</v>
       </c>
-      <c r="F31" s="34"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="49"/>
+      <c r="H31" s="49"/>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B32" s="41"/>
-      <c r="C32" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="D32" s="40"/>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="69"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="D32" s="49"/>
       <c r="E32" s="6">
         <v>170250</v>
       </c>
-      <c r="F32" s="34"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="40"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="49"/>
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B33" s="41"/>
-      <c r="C33" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="D33" s="40"/>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="69"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="D33" s="49"/>
       <c r="E33" s="6">
         <v>491311.95986152801</v>
       </c>
-      <c r="F33" s="34"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="40"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="49"/>
       <c r="I33" s="9"/>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B34" s="41"/>
-      <c r="C34" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="D34" s="40"/>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="69"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="49" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" s="49"/>
       <c r="E34" s="6">
         <v>302954.55181050958</v>
       </c>
-      <c r="F34" s="34"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="49"/>
+      <c r="H34" s="49"/>
       <c r="I34" s="9"/>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B35" s="41"/>
-      <c r="C35" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="D35" s="40"/>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="69"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" s="49"/>
       <c r="E35" s="6">
         <v>230532.45771932101</v>
       </c>
-      <c r="F35" s="34"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="40"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="49"/>
+      <c r="H35" s="49"/>
       <c r="I35" s="9"/>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B36" s="41"/>
-      <c r="C36" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="D36" s="40"/>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="69"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="D36" s="49"/>
       <c r="E36" s="6">
         <v>170250</v>
       </c>
-      <c r="F36" s="34"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="49"/>
+      <c r="H36" s="49"/>
       <c r="I36" s="9"/>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B37" s="41"/>
-      <c r="C37" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="D37" s="40"/>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="69"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="49" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" s="49"/>
       <c r="E37" s="6">
         <v>7118</v>
       </c>
-      <c r="F37" s="34"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="40"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="49"/>
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B38" s="41"/>
-      <c r="C38" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="D38" s="40"/>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="69"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" s="49"/>
       <c r="E38" s="6">
         <v>502.54610000000002</v>
       </c>
-      <c r="F38" s="34"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="40"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="49"/>
+      <c r="H38" s="49"/>
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="41"/>
-      <c r="C39" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="D39" s="40"/>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="69"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="49" t="s">
+        <v>112</v>
+      </c>
+      <c r="D39" s="49"/>
       <c r="E39" s="6">
         <v>0</v>
       </c>
-      <c r="F39" s="34"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="40"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="49"/>
+      <c r="H39" s="49"/>
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="41"/>
-      <c r="C40" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="D40" s="40"/>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="69"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="49" t="s">
+        <v>113</v>
+      </c>
+      <c r="D40" s="49"/>
       <c r="E40" s="6">
         <v>2180772</v>
       </c>
-      <c r="F40" s="34"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="40"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="49"/>
+      <c r="H40" s="49"/>
       <c r="I40" s="9"/>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B41" s="41"/>
-      <c r="C41" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="D41" s="40"/>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="69"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="D41" s="49"/>
       <c r="E41" s="6">
         <v>1155453.8015999999</v>
       </c>
-      <c r="F41" s="34"/>
-      <c r="G41" s="40"/>
-      <c r="H41" s="40"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="49"/>
+      <c r="H41" s="49"/>
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B42" s="41"/>
-      <c r="C42" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="D42" s="40"/>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="69"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="D42" s="49"/>
       <c r="E42" s="6">
         <v>2</v>
       </c>
-      <c r="F42" s="34"/>
-      <c r="G42" s="40"/>
-      <c r="H42" s="40"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="49"/>
+      <c r="H42" s="49"/>
       <c r="I42" s="9"/>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B43" s="41"/>
-      <c r="C43" s="40" t="s">
-        <v>138</v>
-      </c>
-      <c r="D43" s="40"/>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="69"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="D43" s="49"/>
       <c r="E43" s="6">
         <v>2</v>
       </c>
-      <c r="F43" s="34"/>
-      <c r="G43" s="40"/>
-      <c r="H43" s="40"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="49"/>
       <c r="I43" s="9"/>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B44" s="41"/>
-      <c r="C44" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="D44" s="40"/>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="69"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="D44" s="49"/>
       <c r="E44" s="6">
         <v>4</v>
       </c>
-      <c r="F44" s="34"/>
-      <c r="G44" s="40"/>
-      <c r="H44" s="40"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="49"/>
+      <c r="H44" s="49"/>
       <c r="I44" s="9"/>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B45" s="41"/>
-      <c r="C45" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="D45" s="40"/>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="69"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="D45" s="49"/>
       <c r="E45" s="6">
         <v>24</v>
       </c>
-      <c r="F45" s="34"/>
-      <c r="G45" s="40"/>
-      <c r="H45" s="40"/>
+      <c r="F45" s="35"/>
+      <c r="G45" s="49"/>
+      <c r="H45" s="49"/>
       <c r="I45" s="9"/>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B46" s="35" t="s">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="69"/>
+      <c r="B46" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46" s="49"/>
+      <c r="D46" s="49"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="35"/>
+      <c r="G46" s="49"/>
+      <c r="H46" s="49"/>
+      <c r="I46" s="9"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="69"/>
+      <c r="B47" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="C46" s="40"/>
-      <c r="D46" s="40"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="40"/>
-      <c r="H46" s="40"/>
-      <c r="I46" s="9"/>
-    </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B47" s="35" t="s">
+      <c r="C47" s="49"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="35"/>
+      <c r="G47" s="49"/>
+      <c r="H47" s="49"/>
+      <c r="I47" s="9"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="69"/>
+      <c r="B48" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="C47" s="40"/>
-      <c r="D47" s="40"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="40"/>
-      <c r="H47" s="40"/>
-      <c r="I47" s="9"/>
-    </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B48" s="35" t="s">
+      <c r="C48" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="D48" s="49"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="35"/>
+      <c r="G48" s="49"/>
+      <c r="H48" s="49"/>
+      <c r="I48" s="9"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" s="69"/>
+      <c r="B49" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="C48" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="D48" s="40"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="40"/>
-      <c r="H48" s="40"/>
-      <c r="I48" s="9"/>
-    </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B49" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="C49" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="D49" s="40"/>
+      <c r="C49" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="D49" s="49"/>
       <c r="E49" s="6">
         <v>0</v>
       </c>
-      <c r="F49" s="34"/>
-      <c r="G49" s="40"/>
-      <c r="H49" s="40"/>
+      <c r="F49" s="35"/>
+      <c r="G49" s="49"/>
+      <c r="H49" s="49"/>
       <c r="I49" s="9"/>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B50" s="41"/>
-      <c r="C50" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="D50" s="40"/>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="69"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="D50" s="49"/>
       <c r="E50" s="6">
         <v>0</v>
       </c>
-      <c r="F50" s="34"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="40"/>
+      <c r="F50" s="35"/>
+      <c r="G50" s="49"/>
+      <c r="H50" s="49"/>
       <c r="I50" s="9"/>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B51" s="41"/>
-      <c r="C51" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D51" s="40"/>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="69"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="D51" s="49"/>
       <c r="E51" s="6">
         <v>0</v>
       </c>
-      <c r="F51" s="34"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="40"/>
+      <c r="F51" s="35"/>
+      <c r="G51" s="49"/>
+      <c r="H51" s="49"/>
       <c r="I51" s="9"/>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B52" s="41"/>
-      <c r="C52" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="D52" s="40"/>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" s="69"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="D52" s="49"/>
       <c r="E52" s="6">
         <v>0</v>
       </c>
-      <c r="F52" s="34"/>
-      <c r="G52" s="40"/>
-      <c r="H52" s="40"/>
+      <c r="F52" s="35"/>
+      <c r="G52" s="49"/>
+      <c r="H52" s="49"/>
       <c r="I52" s="9"/>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B53" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="C53" s="40"/>
-      <c r="D53" s="40"/>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="69"/>
+      <c r="B53" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" s="49"/>
+      <c r="D53" s="49"/>
       <c r="E53" s="6"/>
-      <c r="F53" s="34"/>
-      <c r="G53" s="40"/>
-      <c r="H53" s="40"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="49"/>
+      <c r="H53" s="49"/>
       <c r="I53" s="9"/>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B54" s="46" t="s">
-        <v>49</v>
-      </c>
-      <c r="C54" s="46"/>
-      <c r="D54" s="46"/>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="69"/>
+      <c r="B54" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="C54" s="50"/>
+      <c r="D54" s="50"/>
       <c r="E54" s="10">
         <f>SUM(E5:E53)</f>
         <v>22063629.317091361</v>
       </c>
-      <c r="F54" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="G54" s="47"/>
-      <c r="H54" s="47"/>
+      <c r="F54" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="G54" s="51"/>
+      <c r="H54" s="51"/>
       <c r="I54" s="11">
         <f>SUM(I5:I53)</f>
         <v>47471370</v>
       </c>
     </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B55" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="C55" s="48"/>
-      <c r="D55" s="48"/>
-      <c r="E55" s="48"/>
-      <c r="F55" s="48"/>
-      <c r="G55" s="48"/>
-      <c r="H55" s="48"/>
-      <c r="I55" s="48"/>
-    </row>
-    <row r="56" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="43">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="69"/>
+      <c r="B55" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C55" s="44"/>
+      <c r="D55" s="44"/>
+      <c r="E55" s="44"/>
+      <c r="F55" s="44"/>
+      <c r="G55" s="44"/>
+      <c r="H55" s="44"/>
+      <c r="I55" s="44"/>
+    </row>
+    <row r="56" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="69"/>
+      <c r="B56" s="45">
         <f>E54-I54</f>
         <v>-25407740.682908639</v>
       </c>
-      <c r="C56" s="43"/>
-      <c r="D56" s="43"/>
-      <c r="E56" s="43"/>
-      <c r="F56" s="43"/>
-      <c r="G56" s="43"/>
-      <c r="H56" s="43"/>
-      <c r="I56" s="43"/>
-    </row>
-    <row r="59" spans="2:9" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B59" s="1" t="s">
+      <c r="C56" s="45"/>
+      <c r="D56" s="45"/>
+      <c r="E56" s="45"/>
+      <c r="F56" s="45"/>
+      <c r="G56" s="45"/>
+      <c r="H56" s="45"/>
+      <c r="I56" s="45"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="69"/>
+      <c r="B57" s="70"/>
+      <c r="C57" s="70"/>
+      <c r="D57" s="70"/>
+      <c r="E57" s="70"/>
+      <c r="F57" s="70"/>
+      <c r="G57" s="70"/>
+      <c r="H57" s="70"/>
+      <c r="I57" s="71"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="69"/>
+      <c r="B58" s="70"/>
+      <c r="C58" s="70"/>
+      <c r="D58" s="70"/>
+      <c r="E58" s="70"/>
+      <c r="F58" s="70"/>
+      <c r="G58" s="70"/>
+      <c r="H58" s="70"/>
+      <c r="I58" s="71"/>
+    </row>
+    <row r="59" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A59" s="69"/>
+      <c r="B59" s="72" t="s">
+        <v>51</v>
+      </c>
+      <c r="C59" s="70"/>
+      <c r="D59" s="70"/>
+      <c r="E59" s="70"/>
+      <c r="F59" s="70"/>
+      <c r="G59" s="70"/>
+      <c r="H59" s="70"/>
+      <c r="I59" s="71"/>
+    </row>
+    <row r="60" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="69"/>
+      <c r="B60" s="70" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="60" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B60" t="s">
+      <c r="C60" s="70"/>
+      <c r="D60" s="70"/>
+      <c r="E60" s="70"/>
+      <c r="F60" s="70"/>
+      <c r="G60" s="70"/>
+      <c r="H60" s="70"/>
+      <c r="I60" s="71"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" s="69"/>
+      <c r="B61" s="12" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B61" s="12" t="s">
+      <c r="C61" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="C61" s="44" t="s">
+      <c r="D61" s="46"/>
+      <c r="E61" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="D61" s="44"/>
-      <c r="E61" s="33" t="s">
+      <c r="F61" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="F61" s="33" t="s">
+      <c r="G61" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="G61" s="33" t="s">
+      <c r="H61" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="H61" s="33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I61" s="71"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" s="69"/>
       <c r="B62" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C62" s="45" t="s">
-        <v>119</v>
-      </c>
-      <c r="D62" s="45"/>
+        <v>61</v>
+      </c>
+      <c r="C62" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="D62" s="40"/>
       <c r="E62" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F62" s="17">
         <v>0</v>
@@ -2082,17 +2384,19 @@
       <c r="H62" s="18">
         <v>69058</v>
       </c>
-    </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I62" s="71"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" s="69"/>
       <c r="B63" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C63" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="D63" s="45"/>
+        <v>61</v>
+      </c>
+      <c r="C63" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="D63" s="40"/>
       <c r="E63" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F63" s="17">
         <v>0</v>
@@ -2103,17 +2407,19 @@
       <c r="H63" s="18">
         <v>69456</v>
       </c>
-    </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I63" s="71"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" s="69"/>
       <c r="B64" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C64" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="D64" s="45"/>
+      <c r="C64" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="D64" s="40"/>
       <c r="E64" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F64" s="17">
         <v>989004166</v>
@@ -2124,17 +2430,19 @@
       <c r="H64" s="18">
         <v>56336</v>
       </c>
-    </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="I64" s="71"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" s="69"/>
       <c r="B65" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C65" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="D65" s="45"/>
+        <v>121</v>
+      </c>
+      <c r="C65" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="D65" s="40"/>
       <c r="E65" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F65" s="17">
         <v>203500000</v>
@@ -2145,88 +2453,119 @@
       <c r="H65" s="18">
         <v>46474</v>
       </c>
-    </row>
-    <row r="66" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="49" t="s">
+      <c r="I65" s="71"/>
+    </row>
+    <row r="66" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="69"/>
+      <c r="B66" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C66" s="50" t="s">
-        <v>63</v>
-      </c>
-      <c r="D66" s="50"/>
-      <c r="E66" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F66" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="G66" s="28"/>
+      <c r="C66" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="D66" s="42"/>
+      <c r="E66" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="F66" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="G66" s="29"/>
       <c r="H66" s="20"/>
-    </row>
-    <row r="67" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="49"/>
-      <c r="C67" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="D67" s="51"/>
-      <c r="E67" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="F67" s="32">
+      <c r="I66" s="71"/>
+    </row>
+    <row r="67" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="69"/>
+      <c r="B67" s="48"/>
+      <c r="C67" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="D67" s="47"/>
+      <c r="E67" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="F67" s="30">
         <f>SUM(F62:F65)</f>
         <v>1192504166</v>
       </c>
-      <c r="G67" s="29"/>
+      <c r="G67" s="31"/>
       <c r="H67" s="23"/>
-    </row>
-    <row r="69" spans="2:10" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B69" s="1" t="s">
+      <c r="I67" s="71"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" s="69"/>
+      <c r="B68" s="70"/>
+      <c r="C68" s="70"/>
+      <c r="D68" s="70"/>
+      <c r="E68" s="70"/>
+      <c r="F68" s="70"/>
+      <c r="G68" s="70"/>
+      <c r="H68" s="70"/>
+      <c r="I68" s="71"/>
+    </row>
+    <row r="69" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A69" s="69"/>
+      <c r="B69" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C69" s="70"/>
+      <c r="D69" s="70"/>
+      <c r="E69" s="70"/>
+      <c r="F69" s="70"/>
+      <c r="G69" s="70"/>
+      <c r="H69" s="70"/>
+      <c r="I69" s="71"/>
+    </row>
+    <row r="70" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="69"/>
+      <c r="B70" s="70" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="70" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B70" t="s">
+      <c r="C70" s="70"/>
+      <c r="D70" s="70"/>
+      <c r="E70" s="70"/>
+      <c r="F70" s="70"/>
+      <c r="G70" s="70"/>
+      <c r="H70" s="70"/>
+      <c r="I70" s="71"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" s="69"/>
+      <c r="B71" s="12" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B71" s="12" t="s">
+      <c r="C71" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="D71" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="E71" s="46"/>
+      <c r="F71" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="D71" s="44" t="s">
-        <v>6</v>
-      </c>
-      <c r="E71" s="44"/>
-      <c r="F71" s="33" t="s">
+      <c r="G71" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="G71" s="33" t="s">
+      <c r="H71" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="H71" s="33" t="s">
+      <c r="I71" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="I71" s="33" t="s">
-        <v>74</v>
-      </c>
-      <c r="J71" s="33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" s="69"/>
       <c r="B72" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C72" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="D72" s="45" t="s">
-        <v>107</v>
-      </c>
-      <c r="E72" s="45"/>
+        <v>124</v>
+      </c>
+      <c r="C72" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="D72" s="40" t="s">
+        <v>105</v>
+      </c>
+      <c r="E72" s="40"/>
       <c r="F72" s="17">
         <v>1946016</v>
       </c>
@@ -2237,19 +2576,19 @@
         <v>38.866998010293848</v>
       </c>
       <c r="I72" s="18"/>
-      <c r="J72" s="18"/>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" s="69"/>
       <c r="B73" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C73" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="D73" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="E73" s="45"/>
+        <v>124</v>
+      </c>
+      <c r="C73" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="D73" s="40" t="s">
+        <v>106</v>
+      </c>
+      <c r="E73" s="40"/>
       <c r="F73" s="17">
         <v>1000001</v>
       </c>
@@ -2260,19 +2599,19 @@
         <v>15.689184310815691</v>
       </c>
       <c r="I73" s="18"/>
-      <c r="J73" s="18"/>
-    </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" s="69"/>
       <c r="B74" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C74" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="D74" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="E74" s="45"/>
+        <v>74</v>
+      </c>
+      <c r="C74" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="D74" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="E74" s="40"/>
       <c r="F74" s="17">
         <v>1831849</v>
       </c>
@@ -2283,19 +2622,19 @@
         <v>6.4607399409012416</v>
       </c>
       <c r="I74" s="18"/>
-      <c r="J74" s="18"/>
-    </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" s="69"/>
       <c r="B75" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C75" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="D75" s="45" t="s">
-        <v>109</v>
-      </c>
-      <c r="E75" s="45"/>
+        <v>74</v>
+      </c>
+      <c r="C75" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="D75" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="E75" s="40"/>
       <c r="F75" s="17">
         <v>143500</v>
       </c>
@@ -2306,19 +2645,19 @@
         <v>18.641114982578401</v>
       </c>
       <c r="I75" s="18"/>
-      <c r="J75" s="18"/>
-    </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" s="69"/>
       <c r="B76" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C76" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="D76" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="E76" s="45"/>
+        <v>74</v>
+      </c>
+      <c r="C76" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="D76" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="E76" s="40"/>
       <c r="F76" s="17">
         <v>1064609</v>
       </c>
@@ -2329,19 +2668,19 @@
         <v>-53.850478451569742</v>
       </c>
       <c r="I76" s="18"/>
-      <c r="J76" s="18"/>
-    </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" s="69"/>
       <c r="B77" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C77" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="D77" s="45" t="s">
-        <v>111</v>
-      </c>
-      <c r="E77" s="45"/>
+        <v>74</v>
+      </c>
+      <c r="C77" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="D77" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="E77" s="40"/>
       <c r="F77" s="17">
         <v>297847</v>
       </c>
@@ -2352,19 +2691,19 @@
         <v>1.714823990340538</v>
       </c>
       <c r="I77" s="18"/>
-      <c r="J77" s="18"/>
-    </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" s="69"/>
       <c r="B78" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C78" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="D78" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="E78" s="45"/>
+        <v>74</v>
+      </c>
+      <c r="C78" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="D78" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="E78" s="40"/>
       <c r="F78" s="17">
         <v>296496</v>
       </c>
@@ -2375,19 +2714,19 @@
         <v>-22.247700569545291</v>
       </c>
       <c r="I78" s="18"/>
-      <c r="J78" s="18"/>
-    </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" s="69"/>
       <c r="B79" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C79" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="D79" s="45" t="s">
-        <v>109</v>
-      </c>
-      <c r="E79" s="45"/>
+        <v>74</v>
+      </c>
+      <c r="C79" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="D79" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="E79" s="40"/>
       <c r="F79" s="17">
         <v>296500</v>
       </c>
@@ -2398,41 +2737,41 @@
         <v>-42.580101180438447</v>
       </c>
       <c r="I79" s="18"/>
-      <c r="J79" s="18"/>
-    </row>
-    <row r="80" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="52" t="s">
+    </row>
+    <row r="80" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="69"/>
+      <c r="B80" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C80" s="28"/>
-      <c r="D80" s="50" t="s">
+      <c r="C80" s="29"/>
+      <c r="D80" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="E80" s="42"/>
+      <c r="F80" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="E80" s="50"/>
-      <c r="F80" s="28" t="s">
+      <c r="G80" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="G80" s="28" t="s">
+      <c r="H80" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="H80" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="I80" s="28"/>
-      <c r="J80" s="20"/>
-    </row>
-    <row r="81" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="52"/>
-      <c r="C81" s="29"/>
-      <c r="D81" s="51" t="s">
-        <v>129</v>
-      </c>
-      <c r="E81" s="51"/>
-      <c r="F81" s="32">
+      <c r="I80" s="20"/>
+    </row>
+    <row r="81" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="69"/>
+      <c r="B81" s="41"/>
+      <c r="C81" s="31"/>
+      <c r="D81" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="E81" s="47"/>
+      <c r="F81" s="30">
         <f>SUM(F72:F79)</f>
         <v>6876818</v>
       </c>
-      <c r="G81" s="32">
+      <c r="G81" s="30">
         <f>SUM(G72:G79)</f>
         <v>7174765.969391359</v>
       </c>
@@ -2440,139 +2779,1307 @@
         <f>(SUM(G72:G79) - SUM(F72:F79)) * 100 / IF(SUM(F72:F79), SUM(F72:F79), 1)</f>
         <v>4.332642937349207</v>
       </c>
-      <c r="I81" s="29"/>
-      <c r="J81" s="23"/>
-    </row>
-    <row r="83" spans="2:10" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B83" s="1" t="s">
+      <c r="I81" s="73"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" s="69"/>
+      <c r="B82" s="70"/>
+      <c r="C82" s="70"/>
+      <c r="D82" s="70"/>
+      <c r="E82" s="70"/>
+      <c r="F82" s="70"/>
+      <c r="G82" s="70"/>
+      <c r="H82" s="70"/>
+      <c r="I82" s="71"/>
+    </row>
+    <row r="83" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A83" s="69"/>
+      <c r="B83" s="72" t="s">
+        <v>81</v>
+      </c>
+      <c r="C83" s="70"/>
+      <c r="D83" s="70"/>
+      <c r="E83" s="70"/>
+      <c r="F83" s="70"/>
+      <c r="G83" s="70"/>
+      <c r="H83" s="70"/>
+      <c r="I83" s="71"/>
+    </row>
+    <row r="84" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="69"/>
+      <c r="B84" s="70" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B84" t="s">
+      <c r="C84" s="70"/>
+      <c r="D84" s="70"/>
+      <c r="E84" s="70"/>
+      <c r="F84" s="70"/>
+      <c r="G84" s="70"/>
+      <c r="H84" s="70"/>
+      <c r="I84" s="71"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A85" s="69"/>
+      <c r="B85" s="26" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B85" s="26" t="s">
+      <c r="C85" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D85" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="E85" s="39"/>
+      <c r="F85" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="D85" s="54" t="s">
-        <v>6</v>
-      </c>
-      <c r="E85" s="54"/>
-      <c r="F85" s="30" t="s">
+      <c r="G85" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="G85" s="30" t="s">
+      <c r="H85" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="H85" s="30" t="s">
+      <c r="I85" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="I85" s="30" t="s">
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A86" s="69"/>
+      <c r="B86" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="J85" s="30" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B86" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="C86" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D86" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="E86" s="45"/>
+      <c r="C86" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="D86" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="E86" s="40"/>
       <c r="F86" s="17">
         <v>0</v>
       </c>
       <c r="G86" s="17">
         <v>47471370</v>
       </c>
-      <c r="H86" s="31"/>
+      <c r="H86" s="33"/>
       <c r="I86" s="18">
         <v>44505</v>
       </c>
-      <c r="J86" s="18">
-        <v>44505</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A87" s="69"/>
       <c r="B87" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="C87" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="D87" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="E87" s="45"/>
+        <v>88</v>
+      </c>
+      <c r="C87" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="D87" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="E87" s="40"/>
       <c r="F87" s="17">
         <v>40000000</v>
       </c>
       <c r="G87" s="17">
         <v>0</v>
       </c>
-      <c r="H87" s="31">
+      <c r="H87" s="33">
         <v>4.87</v>
       </c>
       <c r="I87" s="18">
         <v>43889</v>
       </c>
-      <c r="J87" s="18">
-        <v>46450</v>
-      </c>
-    </row>
-    <row r="88" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="52" t="s">
+    </row>
+    <row r="88" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="69"/>
+      <c r="B88" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C88" s="28"/>
-      <c r="D88" s="50" t="s">
+      <c r="C88" s="29"/>
+      <c r="D88" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="E88" s="42"/>
+      <c r="F88" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="G88" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="E88" s="50"/>
-      <c r="F88" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="G88" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="H88" s="28"/>
-      <c r="I88" s="28"/>
-      <c r="J88" s="20"/>
-    </row>
-    <row r="89" spans="2:10" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B89" s="52"/>
-      <c r="C89" s="29"/>
-      <c r="D89" s="53">
+      <c r="H88" s="29"/>
+      <c r="I88" s="20"/>
+    </row>
+    <row r="89" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="69"/>
+      <c r="B89" s="41"/>
+      <c r="C89" s="31"/>
+      <c r="D89" s="43">
         <f>SUM(2)</f>
         <v>2</v>
       </c>
-      <c r="E89" s="53"/>
-      <c r="F89" s="32">
+      <c r="E89" s="43"/>
+      <c r="F89" s="30">
         <f>SUM(F86:F87)</f>
         <v>40000000</v>
       </c>
-      <c r="G89" s="32">
+      <c r="G89" s="30">
         <f>SUM(G86:G87)</f>
         <v>47471370</v>
       </c>
-      <c r="H89" s="29"/>
-      <c r="I89" s="29"/>
-      <c r="J89" s="23"/>
+      <c r="H89" s="31"/>
+      <c r="I89" s="73"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A90" s="69"/>
+      <c r="B90" s="59"/>
+      <c r="C90" s="60"/>
+      <c r="D90" s="61"/>
+      <c r="E90" s="61"/>
+      <c r="F90" s="58"/>
+      <c r="G90" s="58"/>
+      <c r="H90" s="57"/>
+      <c r="I90" s="74"/>
+    </row>
+    <row r="91" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="75"/>
+      <c r="B91" s="28"/>
+      <c r="C91" s="76"/>
+      <c r="D91" s="77"/>
+      <c r="E91" s="77"/>
+      <c r="F91" s="78"/>
+      <c r="G91" s="78"/>
+      <c r="H91" s="79"/>
+      <c r="I91" s="23"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A92" s="62" t="s">
+        <v>145</v>
+      </c>
+      <c r="B92" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="C92" s="63"/>
+      <c r="D92" s="63"/>
+      <c r="E92" s="63"/>
+      <c r="F92" s="64" t="s">
+        <v>4</v>
+      </c>
+      <c r="G92" s="64"/>
+      <c r="H92" s="64"/>
+      <c r="I92" s="64"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A93" s="62"/>
+      <c r="B93" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C93" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" s="55"/>
+      <c r="E93" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="F93" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="G93" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="H93" s="55"/>
+      <c r="I93" s="37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A94" s="62"/>
+      <c r="B94" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="49"/>
+      <c r="E94" s="6">
+        <v>3931685</v>
+      </c>
+      <c r="F94" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="G94" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="H94" s="49"/>
+      <c r="I94" s="8">
+        <v>600000000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A95" s="62"/>
+      <c r="B95" s="52"/>
+      <c r="C95" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" s="49"/>
+      <c r="E95" s="6">
+        <v>13090630</v>
+      </c>
+      <c r="F95" s="35"/>
+      <c r="G95" s="49"/>
+      <c r="H95" s="49"/>
+      <c r="I95" s="9"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A96" s="62"/>
+      <c r="B96" s="52"/>
+      <c r="C96" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="D96" s="49"/>
+      <c r="E96" s="6">
+        <v>41</v>
+      </c>
+      <c r="F96" s="35"/>
+      <c r="G96" s="49"/>
+      <c r="H96" s="49"/>
+      <c r="I96" s="9"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A97" s="62"/>
+      <c r="B97" s="52"/>
+      <c r="C97" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" s="49"/>
+      <c r="E97" s="6">
+        <v>2</v>
+      </c>
+      <c r="F97" s="35"/>
+      <c r="G97" s="49"/>
+      <c r="H97" s="49"/>
+      <c r="I97" s="9"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A98" s="62"/>
+      <c r="B98" s="52"/>
+      <c r="C98" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D98" s="49"/>
+      <c r="E98" s="6">
+        <v>3269297</v>
+      </c>
+      <c r="F98" s="35"/>
+      <c r="G98" s="49"/>
+      <c r="H98" s="49"/>
+      <c r="I98" s="9"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A99" s="62"/>
+      <c r="B99" s="52"/>
+      <c r="C99" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D99" s="49"/>
+      <c r="E99" s="6">
+        <v>1107</v>
+      </c>
+      <c r="F99" s="35"/>
+      <c r="G99" s="49"/>
+      <c r="H99" s="49"/>
+      <c r="I99" s="9"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A100" s="62"/>
+      <c r="B100" s="52"/>
+      <c r="C100" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="D100" s="49"/>
+      <c r="E100" s="6">
+        <v>126</v>
+      </c>
+      <c r="F100" s="35"/>
+      <c r="G100" s="49"/>
+      <c r="H100" s="49"/>
+      <c r="I100" s="9"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A101" s="62"/>
+      <c r="B101" s="52"/>
+      <c r="C101" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="D101" s="49"/>
+      <c r="E101" s="6">
+        <v>6449648</v>
+      </c>
+      <c r="F101" s="35"/>
+      <c r="G101" s="49"/>
+      <c r="H101" s="49"/>
+      <c r="I101" s="9"/>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A102" s="62"/>
+      <c r="B102" s="52"/>
+      <c r="C102" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102" s="49"/>
+      <c r="E102" s="6">
+        <v>7000</v>
+      </c>
+      <c r="F102" s="35"/>
+      <c r="G102" s="49"/>
+      <c r="H102" s="49"/>
+      <c r="I102" s="9"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A103" s="62"/>
+      <c r="B103" s="52"/>
+      <c r="C103" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="D103" s="49"/>
+      <c r="E103" s="6">
+        <v>41506</v>
+      </c>
+      <c r="F103" s="35"/>
+      <c r="G103" s="49"/>
+      <c r="H103" s="49"/>
+      <c r="I103" s="9"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A104" s="62"/>
+      <c r="B104" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C104" s="49"/>
+      <c r="D104" s="49"/>
+      <c r="E104" s="6"/>
+      <c r="F104" s="35"/>
+      <c r="G104" s="49"/>
+      <c r="H104" s="49"/>
+      <c r="I104" s="9"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A105" s="62"/>
+      <c r="B105" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C105" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D105" s="49"/>
+      <c r="E105" s="6">
+        <v>0</v>
+      </c>
+      <c r="F105" s="35"/>
+      <c r="G105" s="49"/>
+      <c r="H105" s="49"/>
+      <c r="I105" s="9"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A106" s="62"/>
+      <c r="B106" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="C106" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="D106" s="49"/>
+      <c r="E106" s="6">
+        <v>100000</v>
+      </c>
+      <c r="F106" s="35"/>
+      <c r="G106" s="49"/>
+      <c r="H106" s="49"/>
+      <c r="I106" s="9"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A107" s="62"/>
+      <c r="B107" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="C107" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="D107" s="49"/>
+      <c r="E107" s="6">
+        <v>0</v>
+      </c>
+      <c r="F107" s="35"/>
+      <c r="G107" s="49"/>
+      <c r="H107" s="49"/>
+      <c r="I107" s="9"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A108" s="62"/>
+      <c r="B108" s="52"/>
+      <c r="C108" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="D108" s="49"/>
+      <c r="E108" s="6">
+        <v>0</v>
+      </c>
+      <c r="F108" s="35"/>
+      <c r="G108" s="49"/>
+      <c r="H108" s="49"/>
+      <c r="I108" s="9"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A109" s="62"/>
+      <c r="B109" s="52"/>
+      <c r="C109" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="D109" s="49"/>
+      <c r="E109" s="6">
+        <v>12000</v>
+      </c>
+      <c r="F109" s="35"/>
+      <c r="G109" s="49"/>
+      <c r="H109" s="49"/>
+      <c r="I109" s="9"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A110" s="62"/>
+      <c r="B110" s="52"/>
+      <c r="C110" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="D110" s="49"/>
+      <c r="E110" s="6">
+        <v>0</v>
+      </c>
+      <c r="F110" s="35"/>
+      <c r="G110" s="49"/>
+      <c r="H110" s="49"/>
+      <c r="I110" s="9"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A111" s="62"/>
+      <c r="B111" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="C111" s="49" t="s">
+        <v>28</v>
+      </c>
+      <c r="D111" s="49"/>
+      <c r="E111" s="6">
+        <v>1919980</v>
+      </c>
+      <c r="F111" s="35"/>
+      <c r="G111" s="49"/>
+      <c r="H111" s="49"/>
+      <c r="I111" s="9"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A112" s="62"/>
+      <c r="B112" s="52"/>
+      <c r="C112" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="D112" s="49"/>
+      <c r="E112" s="6">
+        <v>1726080</v>
+      </c>
+      <c r="F112" s="35"/>
+      <c r="G112" s="49"/>
+      <c r="H112" s="49"/>
+      <c r="I112" s="9"/>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A113" s="62"/>
+      <c r="B113" s="52"/>
+      <c r="C113" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="D113" s="49"/>
+      <c r="E113" s="6">
+        <v>20105</v>
+      </c>
+      <c r="F113" s="35"/>
+      <c r="G113" s="49"/>
+      <c r="H113" s="49"/>
+      <c r="I113" s="9"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A114" s="62"/>
+      <c r="B114" s="52"/>
+      <c r="C114" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="D114" s="49"/>
+      <c r="E114" s="6">
+        <v>446955.17499999999</v>
+      </c>
+      <c r="F114" s="35"/>
+      <c r="G114" s="49"/>
+      <c r="H114" s="49"/>
+      <c r="I114" s="9"/>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A115" s="62"/>
+      <c r="B115" s="52"/>
+      <c r="C115" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="D115" s="49"/>
+      <c r="E115" s="6">
+        <v>3481.8249999999998</v>
+      </c>
+      <c r="F115" s="35"/>
+      <c r="G115" s="49"/>
+      <c r="H115" s="49"/>
+      <c r="I115" s="9"/>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A116" s="62"/>
+      <c r="B116" s="52"/>
+      <c r="C116" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="D116" s="49"/>
+      <c r="E116" s="6">
+        <v>282</v>
+      </c>
+      <c r="F116" s="35"/>
+      <c r="G116" s="49"/>
+      <c r="H116" s="49"/>
+      <c r="I116" s="9"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A117" s="62"/>
+      <c r="B117" s="52"/>
+      <c r="C117" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="D117" s="49"/>
+      <c r="E117" s="6">
+        <v>693121</v>
+      </c>
+      <c r="F117" s="35"/>
+      <c r="G117" s="49"/>
+      <c r="H117" s="49"/>
+      <c r="I117" s="9"/>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A118" s="62"/>
+      <c r="B118" s="52"/>
+      <c r="C118" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="D118" s="49"/>
+      <c r="E118" s="6">
+        <v>1</v>
+      </c>
+      <c r="F118" s="35"/>
+      <c r="G118" s="49"/>
+      <c r="H118" s="49"/>
+      <c r="I118" s="9"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A119" s="62"/>
+      <c r="B119" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C119" s="49"/>
+      <c r="D119" s="49"/>
+      <c r="E119" s="6"/>
+      <c r="F119" s="35"/>
+      <c r="G119" s="49"/>
+      <c r="H119" s="49"/>
+      <c r="I119" s="9"/>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A120" s="62"/>
+      <c r="B120" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C120" s="49"/>
+      <c r="D120" s="49"/>
+      <c r="E120" s="6"/>
+      <c r="F120" s="35"/>
+      <c r="G120" s="49"/>
+      <c r="H120" s="49"/>
+      <c r="I120" s="9"/>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A121" s="62"/>
+      <c r="B121" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C121" s="49"/>
+      <c r="D121" s="49"/>
+      <c r="E121" s="6"/>
+      <c r="F121" s="35"/>
+      <c r="G121" s="49"/>
+      <c r="H121" s="49"/>
+      <c r="I121" s="9"/>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A122" s="62"/>
+      <c r="B122" s="52" t="s">
+        <v>39</v>
+      </c>
+      <c r="C122" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="D122" s="49"/>
+      <c r="E122" s="6">
+        <v>0</v>
+      </c>
+      <c r="F122" s="35"/>
+      <c r="G122" s="49"/>
+      <c r="H122" s="49"/>
+      <c r="I122" s="9"/>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A123" s="62"/>
+      <c r="B123" s="52"/>
+      <c r="C123" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="D123" s="49"/>
+      <c r="E123" s="6">
+        <v>0</v>
+      </c>
+      <c r="F123" s="35"/>
+      <c r="G123" s="49"/>
+      <c r="H123" s="49"/>
+      <c r="I123" s="9"/>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A124" s="62"/>
+      <c r="B124" s="52"/>
+      <c r="C124" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="D124" s="49"/>
+      <c r="E124" s="6">
+        <v>0</v>
+      </c>
+      <c r="F124" s="35"/>
+      <c r="G124" s="49"/>
+      <c r="H124" s="49"/>
+      <c r="I124" s="9"/>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A125" s="62"/>
+      <c r="B125" s="52"/>
+      <c r="C125" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="D125" s="49"/>
+      <c r="E125" s="6">
+        <v>0</v>
+      </c>
+      <c r="F125" s="35"/>
+      <c r="G125" s="49"/>
+      <c r="H125" s="49"/>
+      <c r="I125" s="9"/>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A126" s="62"/>
+      <c r="B126" s="52"/>
+      <c r="C126" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="D126" s="49"/>
+      <c r="E126" s="6">
+        <v>0</v>
+      </c>
+      <c r="F126" s="35"/>
+      <c r="G126" s="49"/>
+      <c r="H126" s="49"/>
+      <c r="I126" s="9"/>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A127" s="62"/>
+      <c r="B127" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="C127" s="49"/>
+      <c r="D127" s="49"/>
+      <c r="E127" s="6"/>
+      <c r="F127" s="35"/>
+      <c r="G127" s="49"/>
+      <c r="H127" s="49"/>
+      <c r="I127" s="9"/>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A128" s="62"/>
+      <c r="B128" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="C128" s="50"/>
+      <c r="D128" s="50"/>
+      <c r="E128" s="10">
+        <f>SUM(E94:E127)</f>
+        <v>31713048</v>
+      </c>
+      <c r="F128" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="G128" s="51"/>
+      <c r="H128" s="51"/>
+      <c r="I128" s="11">
+        <f>SUM(I94:I127)</f>
+        <v>600000000</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A129" s="62"/>
+      <c r="B129" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C129" s="44"/>
+      <c r="D129" s="44"/>
+      <c r="E129" s="44"/>
+      <c r="F129" s="44"/>
+      <c r="G129" s="44"/>
+      <c r="H129" s="44"/>
+      <c r="I129" s="44"/>
+    </row>
+    <row r="130" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A130" s="62"/>
+      <c r="B130" s="45">
+        <f>E128-I128</f>
+        <v>-568286952</v>
+      </c>
+      <c r="C130" s="45"/>
+      <c r="D130" s="45"/>
+      <c r="E130" s="45"/>
+      <c r="F130" s="45"/>
+      <c r="G130" s="45"/>
+      <c r="H130" s="45"/>
+      <c r="I130" s="45"/>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A131" s="62"/>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A132" s="62"/>
+    </row>
+    <row r="133" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A133" s="62"/>
+      <c r="B133" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A134" s="62"/>
+      <c r="B134" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A135" s="62"/>
+      <c r="B135" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C135" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="D135" s="46"/>
+      <c r="E135" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="F135" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="G135" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="H135" s="34" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A136" s="62"/>
+      <c r="B136" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C136" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="D136" s="40"/>
+      <c r="E136" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="F136" s="17">
+        <v>50000000</v>
+      </c>
+      <c r="G136" s="18">
+        <v>43370</v>
+      </c>
+      <c r="H136" s="18">
+        <v>48849</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A137" s="62"/>
+      <c r="B137" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C137" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="D137" s="40"/>
+      <c r="E137" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="F137" s="17">
+        <v>0</v>
+      </c>
+      <c r="G137" s="18">
+        <v>45294</v>
+      </c>
+      <c r="H137" s="18">
+        <v>47121</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A138" s="62"/>
+      <c r="B138" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C138" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="D138" s="40"/>
+      <c r="E138" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="F138" s="17">
+        <v>60000000</v>
+      </c>
+      <c r="G138" s="18">
+        <v>43399</v>
+      </c>
+      <c r="H138" s="18">
+        <v>401119</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A139" s="62"/>
+      <c r="B139" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C139" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="D139" s="40"/>
+      <c r="E139" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="F139" s="17">
+        <v>10000000</v>
+      </c>
+      <c r="G139" s="18">
+        <v>43077</v>
+      </c>
+      <c r="H139" s="18">
+        <v>50382</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A140" s="62"/>
+      <c r="B140" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C140" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="D140" s="40"/>
+      <c r="E140" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="F140" s="17">
+        <v>776330</v>
+      </c>
+      <c r="G140" s="18">
+        <v>46211</v>
+      </c>
+      <c r="H140" s="18">
+        <v>46576</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A141" s="62"/>
+      <c r="B141" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C141" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="D141" s="42"/>
+      <c r="E141" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="F141" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="G141" s="29"/>
+      <c r="H141" s="20"/>
+    </row>
+    <row r="142" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="62"/>
+      <c r="B142" s="48"/>
+      <c r="C142" s="47" t="s">
+        <v>65</v>
+      </c>
+      <c r="D142" s="47"/>
+      <c r="E142" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="F142" s="30">
+        <f>SUM(F136:F140)</f>
+        <v>120776330</v>
+      </c>
+      <c r="G142" s="31"/>
+      <c r="H142" s="23"/>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A143" s="62"/>
+    </row>
+    <row r="144" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A144" s="62"/>
+      <c r="B144" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A145" s="62"/>
+      <c r="B145" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A146" s="62"/>
+      <c r="B146" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C146" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="D146" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="E146" s="46"/>
+      <c r="F146" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="G146" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="H146" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="I146" s="34" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A147" s="62"/>
+      <c r="B147" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C147" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="D147" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="E147" s="40"/>
+      <c r="F147" s="17">
+        <v>1277189</v>
+      </c>
+      <c r="G147" s="17">
+        <v>1919980</v>
+      </c>
+      <c r="H147" s="24">
+        <v>50.328573139918987</v>
+      </c>
+      <c r="I147" s="18"/>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A148" s="62"/>
+      <c r="B148" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C148" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="D148" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="E148" s="40"/>
+      <c r="F148" s="17">
+        <v>1737959</v>
+      </c>
+      <c r="G148" s="17">
+        <v>1726080</v>
+      </c>
+      <c r="H148" s="24">
+        <v>-0.68350289045944124</v>
+      </c>
+      <c r="I148" s="18"/>
+    </row>
+    <row r="149" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="62"/>
+      <c r="B149" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="C149" s="29"/>
+      <c r="D149" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="E149" s="42"/>
+      <c r="F149" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="G149" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="H149" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="I149" s="29"/>
+    </row>
+    <row r="150" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="62"/>
+      <c r="B150" s="41"/>
+      <c r="C150" s="31"/>
+      <c r="D150" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="E150" s="47"/>
+      <c r="F150" s="30">
+        <f>SUM(F147:F148)</f>
+        <v>3015148</v>
+      </c>
+      <c r="G150" s="30">
+        <f>SUM(G147:G148)</f>
+        <v>3646060</v>
+      </c>
+      <c r="H150" s="25">
+        <f>(SUM(G147:G148) - SUM(F147:F148)) * 100 / IF(SUM(F147:F148), SUM(F147:F148), 1)</f>
+        <v>20.924743992666365</v>
+      </c>
+      <c r="I150" s="31"/>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A151" s="62"/>
+    </row>
+    <row r="152" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A152" s="62"/>
+      <c r="B152" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A153" s="62"/>
+      <c r="B153" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A154" s="62"/>
+      <c r="B154" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C154" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D154" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="E154" s="39"/>
+      <c r="F154" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="G154" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="H154" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="I154" s="32" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A155" s="62"/>
+      <c r="B155" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C155" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="D155" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="E155" s="40"/>
+      <c r="F155" s="17">
+        <v>600000000</v>
+      </c>
+      <c r="G155" s="17">
+        <v>600000000</v>
+      </c>
+      <c r="H155" s="33">
+        <v>4.08</v>
+      </c>
+      <c r="I155" s="18">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A156" s="62"/>
+      <c r="B156" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="C156" s="29"/>
+      <c r="D156" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="E156" s="42"/>
+      <c r="F156" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="G156" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="H156" s="29"/>
+      <c r="I156" s="29"/>
+    </row>
+    <row r="157" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A157" s="62"/>
+      <c r="B157" s="41"/>
+      <c r="C157" s="31"/>
+      <c r="D157" s="43">
+        <f>SUM(1)</f>
+        <v>1</v>
+      </c>
+      <c r="E157" s="43"/>
+      <c r="F157" s="30">
+        <f>SUM(F155)</f>
+        <v>600000000</v>
+      </c>
+      <c r="G157" s="30">
+        <f>SUM(G155)</f>
+        <v>600000000</v>
+      </c>
+      <c r="H157" s="31"/>
+      <c r="I157" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="137">
+  <mergeCells count="239">
+    <mergeCell ref="B149:B150"/>
+    <mergeCell ref="D149:E149"/>
+    <mergeCell ref="D150:E150"/>
+    <mergeCell ref="D154:E154"/>
+    <mergeCell ref="D155:E155"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="D156:E156"/>
+    <mergeCell ref="D157:E157"/>
+    <mergeCell ref="A1:A91"/>
+    <mergeCell ref="A92:A157"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="G125:H125"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="G126:H126"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="G127:H127"/>
+    <mergeCell ref="B128:D128"/>
+    <mergeCell ref="F128:H128"/>
+    <mergeCell ref="B129:I129"/>
+    <mergeCell ref="G117:H117"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="G118:H118"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="G119:H119"/>
+    <mergeCell ref="C120:D120"/>
+    <mergeCell ref="G120:H120"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="G121:H121"/>
+    <mergeCell ref="F92:I92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="G93:H93"/>
+    <mergeCell ref="B94:B103"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="G94:H94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="G96:H96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="G103:H103"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="B107:B110"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="B111:B118"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="B141:B142"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="D146:E146"/>
+    <mergeCell ref="D147:E147"/>
+    <mergeCell ref="D148:E148"/>
+    <mergeCell ref="B130:I130"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="B122:B126"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="G122:H122"/>
+    <mergeCell ref="C123:D123"/>
+    <mergeCell ref="G123:H123"/>
+    <mergeCell ref="C124:D124"/>
+    <mergeCell ref="G124:H124"/>
+    <mergeCell ref="G111:H111"/>
+    <mergeCell ref="G112:H112"/>
+    <mergeCell ref="G113:H113"/>
+    <mergeCell ref="G114:H114"/>
+    <mergeCell ref="G115:H115"/>
+    <mergeCell ref="G116:H116"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="G104:H104"/>
+    <mergeCell ref="G105:H105"/>
+    <mergeCell ref="G106:H106"/>
+    <mergeCell ref="G107:H107"/>
+    <mergeCell ref="G108:H108"/>
+    <mergeCell ref="G109:H109"/>
+    <mergeCell ref="G110:H110"/>
     <mergeCell ref="B88:B89"/>
     <mergeCell ref="D88:E88"/>
     <mergeCell ref="D89:E89"/>
@@ -2719,637 +4226,628 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:L68"/>
+  <dimension ref="B1:I68"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.75" customWidth="1"/>
-    <col min="2" max="18" width="16.75" customWidth="1"/>
+    <col min="3" max="3" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="53" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="37" t="s">
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="55"/>
+      <c r="E4" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="D4" s="39"/>
-      <c r="E4" s="3" t="s">
-        <v>7</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="39" t="s">
+      <c r="G4" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="55"/>
+      <c r="I4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="39"/>
-      <c r="I4" s="3" t="s">
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="52" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="41" t="s">
+      <c r="C5" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="40"/>
+      <c r="D5" s="49"/>
       <c r="E5" s="6">
         <v>3931685</v>
       </c>
       <c r="F5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="49" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="40" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="40"/>
+      <c r="H5" s="49"/>
       <c r="I5" s="8">
         <v>600000000</v>
       </c>
-      <c r="K5" s="55">
-        <f>SUM(E5:E14)+100000</f>
-        <v>26891042</v>
-      </c>
-      <c r="L5" s="55">
-        <f>SUM('뱅샐현황(재은)'!E5:E21)</f>
-        <v>11500320</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="41"/>
-      <c r="C6" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="40"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="52"/>
+      <c r="C6" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="49"/>
       <c r="E6" s="6">
         <v>13090630</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="41"/>
-      <c r="C7" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="40"/>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="52"/>
+      <c r="C7" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="49"/>
       <c r="E7" s="6">
         <v>41</v>
       </c>
       <c r="F7" s="5"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="41"/>
-      <c r="C8" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="40"/>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="52"/>
+      <c r="C8" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="49"/>
       <c r="E8" s="6">
         <v>2</v>
       </c>
       <c r="F8" s="5"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="41"/>
-      <c r="C9" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="40"/>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="52"/>
+      <c r="C9" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="49"/>
       <c r="E9" s="6">
         <v>3269297</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="41"/>
-      <c r="C10" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="40"/>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="52"/>
+      <c r="C10" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="49"/>
       <c r="E10" s="6">
         <v>1107</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="41"/>
-      <c r="C11" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="40"/>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B11" s="52"/>
+      <c r="C11" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="49"/>
       <c r="E11" s="6">
         <v>126</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="41"/>
-      <c r="C12" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="40"/>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B12" s="52"/>
+      <c r="C12" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="49"/>
       <c r="E12" s="6">
         <v>6449648</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="41"/>
-      <c r="C13" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="40"/>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B13" s="52"/>
+      <c r="C13" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="49"/>
       <c r="E13" s="6">
         <v>7000</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="41"/>
-      <c r="C14" s="40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="40"/>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B14" s="52"/>
+      <c r="C14" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="49"/>
       <c r="E14" s="6">
         <v>41506</v>
       </c>
       <c r="F14" s="5"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
       <c r="I14" s="9"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
+        <v>17</v>
+      </c>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
       <c r="E15" s="6"/>
       <c r="F15" s="5"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="40"/>
+      <c r="D16" s="49"/>
       <c r="E16" s="6">
         <v>0</v>
       </c>
       <c r="F16" s="5"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
       <c r="I16" s="9"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="40"/>
+      <c r="D17" s="49"/>
       <c r="E17" s="6">
         <v>100000</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="49"/>
       <c r="I17" s="9"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="40"/>
+      <c r="D18" s="49"/>
       <c r="E18" s="6">
         <v>0</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="49"/>
       <c r="I18" s="9"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="41"/>
-      <c r="C19" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="40"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="49"/>
       <c r="E19" s="6">
         <v>0</v>
       </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="49"/>
       <c r="I19" s="9"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="41"/>
-      <c r="C20" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="40"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="49"/>
       <c r="E20" s="6">
         <v>12000</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
       <c r="I20" s="9"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B21" s="41"/>
-      <c r="C21" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21" s="40"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="49"/>
       <c r="E21" s="6">
         <v>0</v>
       </c>
       <c r="F21" s="5"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="49"/>
       <c r="I21" s="9"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="40"/>
+      <c r="D22" s="49"/>
       <c r="E22" s="6">
         <v>1919980</v>
       </c>
       <c r="F22" s="5"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="49"/>
       <c r="I22" s="9"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="41"/>
-      <c r="C23" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="40"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="49" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="49"/>
       <c r="E23" s="6">
         <v>1726080</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
       <c r="I23" s="9"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B24" s="41"/>
-      <c r="C24" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" s="40"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="49"/>
       <c r="E24" s="6">
         <v>20105</v>
       </c>
       <c r="F24" s="5"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="49"/>
       <c r="I24" s="9"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B25" s="41"/>
-      <c r="C25" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="40"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="49" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="49"/>
       <c r="E25" s="6">
         <v>446955.17499999999</v>
       </c>
       <c r="F25" s="5"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="49"/>
       <c r="I25" s="9"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B26" s="41"/>
-      <c r="C26" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" s="40"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="49"/>
       <c r="E26" s="6">
         <v>3481.8249999999998</v>
       </c>
       <c r="F26" s="5"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
       <c r="I26" s="9"/>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B27" s="41"/>
-      <c r="C27" s="40" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" s="40"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" s="49"/>
       <c r="E27" s="6">
         <v>282</v>
       </c>
       <c r="F27" s="5"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="49"/>
       <c r="I27" s="9"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B28" s="41"/>
-      <c r="C28" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" s="40"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="49"/>
       <c r="E28" s="6">
         <v>693121</v>
       </c>
       <c r="F28" s="5"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="49"/>
       <c r="I28" s="9"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B29" s="41"/>
-      <c r="C29" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="D29" s="40"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="49"/>
       <c r="E29" s="6">
         <v>1</v>
       </c>
       <c r="F29" s="5"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="40"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="49"/>
       <c r="I29" s="9"/>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="40"/>
-      <c r="D30" s="40"/>
+        <v>36</v>
+      </c>
+      <c r="C30" s="49"/>
+      <c r="D30" s="49"/>
       <c r="E30" s="6"/>
       <c r="F30" s="5"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
+      <c r="G30" s="49"/>
+      <c r="H30" s="49"/>
       <c r="I30" s="9"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
+        <v>37</v>
+      </c>
+      <c r="C31" s="49"/>
+      <c r="D31" s="49"/>
       <c r="E31" s="6"/>
       <c r="F31" s="5"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
+      <c r="G31" s="49"/>
+      <c r="H31" s="49"/>
       <c r="I31" s="9"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="40"/>
-      <c r="D32" s="40"/>
+        <v>38</v>
+      </c>
+      <c r="C32" s="49"/>
+      <c r="D32" s="49"/>
       <c r="E32" s="6"/>
       <c r="F32" s="5"/>
-      <c r="G32" s="40"/>
-      <c r="H32" s="40"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="49"/>
       <c r="I32" s="9"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B33" s="41" t="s">
+      <c r="B33" s="52" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="40" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" s="40"/>
+      <c r="D33" s="49"/>
       <c r="E33" s="6">
         <v>0</v>
       </c>
       <c r="F33" s="5"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="40"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="49"/>
       <c r="I33" s="9"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B34" s="41"/>
-      <c r="C34" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="D34" s="40"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" s="49"/>
       <c r="E34" s="6">
         <v>0</v>
       </c>
       <c r="F34" s="5"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
+      <c r="G34" s="49"/>
+      <c r="H34" s="49"/>
       <c r="I34" s="9"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B35" s="41"/>
-      <c r="C35" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" s="40"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="D35" s="49"/>
       <c r="E35" s="6">
         <v>0</v>
       </c>
       <c r="F35" s="5"/>
-      <c r="G35" s="40"/>
-      <c r="H35" s="40"/>
+      <c r="G35" s="49"/>
+      <c r="H35" s="49"/>
       <c r="I35" s="9"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B36" s="41"/>
-      <c r="C36" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="40"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" s="49"/>
       <c r="E36" s="6">
         <v>0</v>
       </c>
       <c r="F36" s="5"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="40"/>
+      <c r="G36" s="49"/>
+      <c r="H36" s="49"/>
       <c r="I36" s="9"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B37" s="41"/>
-      <c r="C37" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="D37" s="40"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="49"/>
       <c r="E37" s="6">
         <v>0</v>
       </c>
       <c r="F37" s="5"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="40"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="49"/>
       <c r="I37" s="9"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
+        <v>45</v>
+      </c>
+      <c r="C38" s="49"/>
+      <c r="D38" s="49"/>
       <c r="E38" s="6"/>
       <c r="F38" s="5"/>
-      <c r="G38" s="40"/>
-      <c r="H38" s="40"/>
+      <c r="G38" s="49"/>
+      <c r="H38" s="49"/>
       <c r="I38" s="9"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="46" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46"/>
+      <c r="B39" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" s="50"/>
+      <c r="D39" s="50"/>
       <c r="E39" s="10">
         <f>SUM(E5:E38)</f>
         <v>31713048</v>
       </c>
-      <c r="F39" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="G39" s="47"/>
-      <c r="H39" s="47"/>
+      <c r="F39" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="G39" s="51"/>
+      <c r="H39" s="51"/>
       <c r="I39" s="11">
         <f>SUM(I5:I38)</f>
         <v>600000000</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="C40" s="48"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="48"/>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B41" s="43">
+      <c r="B40" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="44"/>
+      <c r="F40" s="44"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="44"/>
+    </row>
+    <row r="41" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="45">
         <f>E39-I39</f>
         <v>-568286952</v>
       </c>
-      <c r="C41" s="43"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="43"/>
-      <c r="I41" s="43"/>
+      <c r="C41" s="45"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="45"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="45"/>
+      <c r="I41" s="45"/>
     </row>
     <row r="44" spans="2:9" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B44" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B45" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B45" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B46" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="C46" s="44" t="s">
+      <c r="D46" s="46"/>
+      <c r="E46" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D46" s="44"/>
-      <c r="E46" s="13" t="s">
+      <c r="F46" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="F46" s="13" t="s">
+      <c r="G46" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="G46" s="13" t="s">
+      <c r="H46" s="13" t="s">
         <v>58</v>
-      </c>
-      <c r="H46" s="13" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B47" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C47" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="D47" s="40"/>
+      <c r="E47" s="16" t="s">
         <v>60</v>
-      </c>
-      <c r="C47" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="D47" s="45"/>
-      <c r="E47" s="16" t="s">
-        <v>61</v>
       </c>
       <c r="F47" s="17">
         <v>50000000</v>
@@ -3363,14 +4861,14 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C48" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="D48" s="45"/>
+        <v>61</v>
+      </c>
+      <c r="C48" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="D48" s="40"/>
       <c r="E48" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F48" s="17">
         <v>0</v>
@@ -3382,16 +4880,16 @@
         <v>47121</v>
       </c>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B49" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="D49" s="40"/>
+      <c r="E49" s="16" t="s">
         <v>60</v>
-      </c>
-      <c r="C49" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="D49" s="45"/>
-      <c r="E49" s="16" t="s">
-        <v>61</v>
       </c>
       <c r="F49" s="17">
         <v>60000000</v>
@@ -3403,16 +4901,16 @@
         <v>401119</v>
       </c>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B50" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="D50" s="40"/>
+      <c r="E50" s="16" t="s">
         <v>60</v>
-      </c>
-      <c r="C50" s="45" t="s">
-        <v>44</v>
-      </c>
-      <c r="D50" s="45"/>
-      <c r="E50" s="16" t="s">
-        <v>61</v>
       </c>
       <c r="F50" s="17">
         <v>10000000</v>
@@ -3424,16 +4922,16 @@
         <v>50382</v>
       </c>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B51" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C51" s="45" t="s">
-        <v>45</v>
-      </c>
-      <c r="D51" s="45"/>
+        <v>61</v>
+      </c>
+      <c r="C51" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="D51" s="40"/>
       <c r="E51" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F51" s="17">
         <v>776330</v>
@@ -3445,31 +4943,31 @@
         <v>46576</v>
       </c>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B52" s="49" t="s">
+    <row r="52" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C52" s="50" t="s">
+      <c r="C52" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="D52" s="42"/>
+      <c r="E52" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="D52" s="50"/>
-      <c r="E52" s="19" t="s">
+      <c r="F52" s="19" t="s">
         <v>64</v>
-      </c>
-      <c r="F52" s="19" t="s">
-        <v>65</v>
       </c>
       <c r="G52" s="19"/>
       <c r="H52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B53" s="49"/>
-      <c r="C53" s="51" t="s">
+    <row r="53" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="48"/>
+      <c r="C53" s="47" t="s">
+        <v>65</v>
+      </c>
+      <c r="D53" s="47"/>
+      <c r="E53" s="21" t="s">
         <v>66</v>
-      </c>
-      <c r="D53" s="51"/>
-      <c r="E53" s="21" t="s">
-        <v>67</v>
       </c>
       <c r="F53" s="22">
         <f>SUM(F47:F51)</f>
@@ -3478,54 +4976,51 @@
       <c r="G53" s="21"/>
       <c r="H53" s="23"/>
     </row>
-    <row r="55" spans="2:10" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:9" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B55" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B56" t="s">
+    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B57" s="12" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B57" s="12" t="s">
+      <c r="C57" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D57" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="46"/>
+      <c r="F57" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C57" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D57" s="44" t="s">
-        <v>6</v>
-      </c>
-      <c r="E57" s="44"/>
-      <c r="F57" s="13" t="s">
+      <c r="G57" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="G57" s="13" t="s">
+      <c r="H57" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="H57" s="13" t="s">
+      <c r="I57" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="I57" s="13" t="s">
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B58" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="J57" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B58" s="14" t="s">
+      <c r="C58" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C58" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="D58" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="E58" s="45"/>
+      <c r="D58" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="E58" s="40"/>
       <c r="F58" s="17">
         <v>1277189</v>
       </c>
@@ -3536,19 +5031,18 @@
         <v>50.328573139918987</v>
       </c>
       <c r="I58" s="18"/>
-      <c r="J58" s="18"/>
-    </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C59" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="C59" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="D59" s="45" t="s">
-        <v>30</v>
-      </c>
-      <c r="E59" s="45"/>
+      <c r="D59" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="E59" s="40"/>
       <c r="F59" s="17">
         <v>1737959</v>
       </c>
@@ -3559,36 +5053,34 @@
         <v>-0.68350289045944124</v>
       </c>
       <c r="I59" s="18"/>
-      <c r="J59" s="18"/>
-    </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B60" s="52" t="s">
+    </row>
+    <row r="60" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B60" s="41" t="s">
         <v>1</v>
       </c>
       <c r="C60" s="19"/>
-      <c r="D60" s="50" t="s">
+      <c r="D60" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="E60" s="42"/>
+      <c r="F60" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E60" s="50"/>
-      <c r="F60" s="19" t="s">
+      <c r="G60" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="G60" s="19" t="s">
+      <c r="H60" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H60" s="19" t="s">
+      <c r="I60" s="19"/>
+    </row>
+    <row r="61" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B61" s="41"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="47" t="s">
         <v>80</v>
       </c>
-      <c r="I60" s="19"/>
-      <c r="J60" s="20"/>
-    </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B61" s="52"/>
-      <c r="C61" s="21"/>
-      <c r="D61" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="E61" s="51"/>
+      <c r="E61" s="47"/>
       <c r="F61" s="22">
         <f>SUM(F58:F59)</f>
         <v>3015148</v>
@@ -3602,56 +5094,52 @@
         <v>20.924743992666365</v>
       </c>
       <c r="I61" s="21"/>
-      <c r="J61" s="23"/>
-    </row>
-    <row r="63" spans="2:10" ht="20.25" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="2:9" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B63" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B64" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B64" t="s">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B65" s="26" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B65" s="26" t="s">
+      <c r="C65" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="D65" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="E65" s="39"/>
+      <c r="F65" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="C65" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="D65" s="54" t="s">
-        <v>6</v>
-      </c>
-      <c r="E65" s="54"/>
-      <c r="F65" s="27" t="s">
+      <c r="G65" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="G65" s="27" t="s">
+      <c r="H65" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="H65" s="27" t="s">
+      <c r="I65" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="I65" s="27" t="s">
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B66" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="J65" s="27" t="s">
+      <c r="C66" s="15" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B66" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="C66" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D66" s="45" t="s">
-        <v>48</v>
-      </c>
-      <c r="E66" s="45"/>
+      <c r="D66" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="E66" s="40"/>
       <c r="F66" s="17">
         <v>600000000</v>
       </c>
@@ -3664,37 +5152,33 @@
       <c r="I66" s="18">
         <v>46192</v>
       </c>
-      <c r="J66" s="18">
-        <v>57123</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B67" s="52" t="s">
+    </row>
+    <row r="67" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B67" s="41" t="s">
         <v>1</v>
       </c>
       <c r="C67" s="19"/>
-      <c r="D67" s="50" t="s">
+      <c r="D67" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="E67" s="42"/>
+      <c r="F67" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G67" s="19" t="s">
         <v>92</v>
-      </c>
-      <c r="E67" s="50"/>
-      <c r="F67" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="G67" s="19" t="s">
-        <v>94</v>
       </c>
       <c r="H67" s="19"/>
       <c r="I67" s="19"/>
-      <c r="J67" s="20"/>
-    </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B68" s="52"/>
+    </row>
+    <row r="68" spans="2:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B68" s="41"/>
       <c r="C68" s="21"/>
-      <c r="D68" s="53">
+      <c r="D68" s="43">
         <f>SUM(1)</f>
         <v>1</v>
       </c>
-      <c r="E68" s="53"/>
+      <c r="E68" s="43"/>
       <c r="F68" s="22">
         <f>SUM(F66)</f>
         <v>600000000</v>
@@ -3705,64 +5189,54 @@
       </c>
       <c r="H68" s="21"/>
       <c r="I68" s="21"/>
-      <c r="J68" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="D59:E59"/>
     <mergeCell ref="D66:E66"/>
     <mergeCell ref="B67:B68"/>
     <mergeCell ref="D67:E67"/>
     <mergeCell ref="D68:E68"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D59:E59"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="B41:I41"/>
     <mergeCell ref="C46:D46"/>
     <mergeCell ref="C47:D47"/>
     <mergeCell ref="C48:D48"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
     <mergeCell ref="G38:H38"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="F39:H39"/>
     <mergeCell ref="C38:D38"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
     <mergeCell ref="G19:H19"/>
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="G34:H34"/>
     <mergeCell ref="G35:H35"/>
     <mergeCell ref="G36:H36"/>
     <mergeCell ref="G23:H23"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="G30:H30"/>
     <mergeCell ref="G31:H31"/>
@@ -3770,29 +5244,28 @@
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="C32:D32"/>
-    <mergeCell ref="B33:B37"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="B22:B29"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="F3:I3"/>
     <mergeCell ref="C4:D4"/>
@@ -3802,16 +5275,25 @@
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="B33:B37"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G8:H8"/>
     <mergeCell ref="G14:H14"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>